--- a/inputs/data/data.xlsx
+++ b/inputs/data/data.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,7 +456,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44562</v>
+        <v>43831</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -465,18 +465,18 @@
         <v>0.19</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44593</v>
+        <v>43862</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -485,38 +485,38 @@
         <v>0.146</v>
       </c>
       <c r="D3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44621</v>
+        <v>43891</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
         <v>0.217</v>
       </c>
       <c r="D4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44652</v>
+        <v>43922</v>
       </c>
       <c r="B5" t="n">
         <v>30</v>
@@ -525,21 +525,21 @@
         <v>0.294</v>
       </c>
       <c r="D5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44682</v>
+        <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
         <v>0.509</v>
@@ -548,135 +548,135 @@
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44713</v>
+        <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C7" t="n">
         <v>0.772</v>
       </c>
       <c r="D7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F7" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44743</v>
+        <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F8" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44774</v>
+        <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>0.861</v>
       </c>
       <c r="D9" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44805</v>
+        <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
         <v>0.509</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>6.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44835</v>
+        <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
         <v>0.242</v>
       </c>
       <c r="D11" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44866</v>
+        <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
         <v>0.163</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44896</v>
+        <v>44166</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -685,18 +685,18 @@
         <v>0.163</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E13" t="n">
         <v>16</v>
       </c>
       <c r="F13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44927</v>
+        <v>44197</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -705,18 +705,18 @@
         <v>0.218</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44958</v>
+        <v>44228</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -725,87 +725,87 @@
         <v>0.043</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44986</v>
+        <v>44256</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C16" t="n">
         <v>0.055</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45017</v>
+        <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C17" t="n">
         <v>0.144</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45047</v>
+        <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C18" t="n">
         <v>0.453</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45078</v>
+        <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
         <v>0.8090000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E19" t="n">
         <v>27</v>
@@ -816,7 +816,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45108</v>
+        <v>44378</v>
       </c>
       <c r="B20" t="n">
         <v>14</v>
@@ -825,98 +825,98 @@
         <v>0.799</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E20" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="F20" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45139</v>
+        <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C21" t="n">
         <v>0.658</v>
       </c>
       <c r="D21" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45170</v>
+        <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C22" t="n">
         <v>0.624</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E22" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45200</v>
+        <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C23" t="n">
         <v>0.132</v>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="E23" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45231</v>
+        <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C24" t="n">
         <v>0.148</v>
       </c>
       <c r="D24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F24" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45261</v>
+        <v>44531</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -925,18 +925,18 @@
         <v>0.021</v>
       </c>
       <c r="D25" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F25" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45292</v>
+        <v>44562</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -945,18 +945,18 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45323</v>
+        <v>44593</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -965,21 +965,21 @@
         <v>0.13</v>
       </c>
       <c r="D27" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45352</v>
+        <v>44621</v>
       </c>
       <c r="B28" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C28" t="n">
         <v>0.024</v>
@@ -991,15 +991,15 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45383</v>
+        <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C29" t="n">
         <v>0.141</v>
@@ -1008,15 +1008,15 @@
         <v>21</v>
       </c>
       <c r="E29" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45413</v>
+        <v>44682</v>
       </c>
       <c r="B30" t="n">
         <v>30</v>
@@ -1025,38 +1025,38 @@
         <v>0.408</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F30" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45444</v>
+        <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C31" t="n">
         <v>0.6860000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F31" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45474</v>
+        <v>44743</v>
       </c>
       <c r="B32" t="n">
         <v>30</v>
@@ -1065,98 +1065,98 @@
         <v>0.753</v>
       </c>
       <c r="D32" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E32" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F32" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45505</v>
+        <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C33" t="n">
         <v>0.854</v>
       </c>
       <c r="D33" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E33" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F33" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45536</v>
+        <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C34" t="n">
         <v>0.449</v>
       </c>
       <c r="D34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F34" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45566</v>
+        <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C35" t="n">
         <v>0.017</v>
       </c>
       <c r="D35" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E35" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45597</v>
+        <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C36" t="n">
         <v>0.17</v>
       </c>
       <c r="D36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E36" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45627</v>
+        <v>44896</v>
       </c>
       <c r="B37" t="n">
         <v>0</v>
@@ -1165,13 +1165,493 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="D37" t="n">
+        <v>16</v>
+      </c>
+      <c r="E37" t="n">
+        <v>32</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>22</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B40" t="n">
+        <v>28</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="D40" t="n">
+        <v>17</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B41" t="n">
+        <v>30</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="D41" t="n">
+        <v>21</v>
+      </c>
+      <c r="E41" t="n">
+        <v>26</v>
+      </c>
+      <c r="F41" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B42" t="n">
+        <v>30</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>32</v>
+      </c>
+      <c r="F42" t="n">
+        <v>5.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B43" t="n">
+        <v>30</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="D43" t="n">
+        <v>20</v>
+      </c>
+      <c r="E43" t="n">
+        <v>28</v>
+      </c>
+      <c r="F43" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B44" t="n">
+        <v>30</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="D44" t="n">
+        <v>21</v>
+      </c>
+      <c r="E44" t="n">
+        <v>30</v>
+      </c>
+      <c r="F44" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B45" t="n">
+        <v>20</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="D45" t="n">
+        <v>13</v>
+      </c>
+      <c r="E45" t="n">
+        <v>29</v>
+      </c>
+      <c r="F45" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B46" t="n">
+        <v>18</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>21</v>
+      </c>
+      <c r="F46" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B47" t="n">
+        <v>26</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="D47" t="n">
+        <v>14</v>
+      </c>
+      <c r="E47" t="n">
+        <v>18</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B48" t="n">
+        <v>30</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="D48" t="n">
+        <v>13</v>
+      </c>
+      <c r="E48" t="n">
+        <v>28</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="D49" t="n">
+        <v>28</v>
+      </c>
+      <c r="E49" t="n">
+        <v>29</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="D51" t="n">
         <v>25</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B52" t="n">
         <v>28</v>
       </c>
-      <c r="F37" t="n">
+      <c r="C52" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="D52" t="n">
+        <v>16</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B53" t="n">
+        <v>30</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="D53" t="n">
+        <v>23</v>
+      </c>
+      <c r="E53" t="n">
+        <v>29</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B54" t="n">
+        <v>30</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>32</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B55" t="n">
+        <v>28</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="D55" t="n">
+        <v>22</v>
+      </c>
+      <c r="E55" t="n">
+        <v>28</v>
+      </c>
+      <c r="F55" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B56" t="n">
+        <v>27</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="D56" t="n">
+        <v>20</v>
+      </c>
+      <c r="E56" t="n">
+        <v>30</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B57" t="n">
+        <v>22</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="D57" t="n">
+        <v>19</v>
+      </c>
+      <c r="E57" t="n">
+        <v>30</v>
+      </c>
+      <c r="F57" t="n">
         <v>3.3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B58" t="n">
+        <v>26</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>23</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B59" t="n">
+        <v>30</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="D59" t="n">
+        <v>27</v>
+      </c>
+      <c r="E59" t="n">
+        <v>30</v>
+      </c>
+      <c r="F59" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B60" t="n">
+        <v>21</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D60" t="n">
+        <v>25</v>
+      </c>
+      <c r="E60" t="n">
+        <v>28</v>
+      </c>
+      <c r="F60" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="D61" t="n">
+        <v>27</v>
+      </c>
+      <c r="E61" t="n">
+        <v>19</v>
+      </c>
+      <c r="F61" t="n">
+        <v>5.8</v>
       </c>
     </row>
   </sheetData>
@@ -1185,7 +1665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1222,7 +1702,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44562</v>
+        <v>43831</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -1231,18 +1711,18 @@
         <v>0.19</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44593</v>
+        <v>43862</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -1251,58 +1731,58 @@
         <v>0.146</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44621</v>
+        <v>43891</v>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>0.217</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44652</v>
+        <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
         <v>0.294</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44682</v>
+        <v>43952</v>
       </c>
       <c r="B6" t="n">
         <v>12</v>
@@ -1311,18 +1791,18 @@
         <v>0.509</v>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44713</v>
+        <v>43983</v>
       </c>
       <c r="B7" t="n">
         <v>12</v>
@@ -1331,30 +1811,30 @@
         <v>0.772</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>7.7</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44743</v>
+        <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="n">
         <v>8.5</v>
@@ -1362,87 +1842,87 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44774</v>
+        <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
         <v>0.861</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44805</v>
+        <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
         <v>0.509</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" t="n">
         <v>9</v>
       </c>
       <c r="F10" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44835</v>
+        <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
         <v>0.242</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="n">
-        <v>6.2</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44866</v>
+        <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
         <v>0.163</v>
       </c>
       <c r="D12" t="n">
+        <v>19</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
         <v>8</v>
-      </c>
-      <c r="E12" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44896</v>
+        <v>44166</v>
       </c>
       <c r="B13" t="n">
         <v>0</v>
@@ -1451,18 +1931,18 @@
         <v>0.163</v>
       </c>
       <c r="D13" t="n">
+        <v>16</v>
+      </c>
+      <c r="E13" t="n">
         <v>9</v>
       </c>
-      <c r="E13" t="n">
-        <v>7</v>
-      </c>
       <c r="F13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44927</v>
+        <v>44197</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -1471,18 +1951,18 @@
         <v>0.218</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>7.3</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44958</v>
+        <v>44228</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -1491,38 +1971,38 @@
         <v>0.043</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44986</v>
+        <v>44256</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
         <v>0.055</v>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45017</v>
+        <v>44287</v>
       </c>
       <c r="B17" t="n">
         <v>15</v>
@@ -1531,101 +2011,101 @@
         <v>0.144</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F17" t="n">
-        <v>8.300000000000001</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45047</v>
+        <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>0.453</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F18" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45078</v>
+        <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
         <v>0.8090000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45108</v>
+        <v>44378</v>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
         <v>0.799</v>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F20" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45139</v>
+        <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C21" t="n">
         <v>0.658</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F21" t="n">
-        <v>8.800000000000001</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45170</v>
+        <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
         <v>0.624</v>
@@ -1634,18 +2114,18 @@
         <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45200</v>
+        <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C23" t="n">
         <v>0.132</v>
@@ -1654,35 +2134,35 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F23" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45231</v>
+        <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24" t="n">
         <v>0.148</v>
       </c>
       <c r="D24" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F24" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45261</v>
+        <v>44531</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -1691,18 +2171,18 @@
         <v>0.021</v>
       </c>
       <c r="D25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45292</v>
+        <v>44562</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -1711,18 +2191,18 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45323</v>
+        <v>44593</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -1731,18 +2211,18 @@
         <v>0.13</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45352</v>
+        <v>44621</v>
       </c>
       <c r="B28" t="n">
         <v>15</v>
@@ -1751,18 +2231,18 @@
         <v>0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45383</v>
+        <v>44652</v>
       </c>
       <c r="B29" t="n">
         <v>15</v>
@@ -1771,18 +2251,18 @@
         <v>0.141</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F29" t="n">
-        <v>8.699999999999999</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45413</v>
+        <v>44682</v>
       </c>
       <c r="B30" t="n">
         <v>15</v>
@@ -1791,18 +2271,18 @@
         <v>0.408</v>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F30" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45444</v>
+        <v>44713</v>
       </c>
       <c r="B31" t="n">
         <v>14</v>
@@ -1811,78 +2291,78 @@
         <v>0.6860000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E31" t="n">
         <v>14</v>
       </c>
       <c r="F31" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45474</v>
+        <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C32" t="n">
         <v>0.753</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F32" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45505</v>
+        <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C33" t="n">
         <v>0.854</v>
       </c>
       <c r="D33" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F33" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45536</v>
+        <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C34" t="n">
         <v>0.449</v>
       </c>
       <c r="D34" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E34" t="n">
         <v>12</v>
       </c>
       <c r="F34" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45566</v>
+        <v>44835</v>
       </c>
       <c r="B35" t="n">
         <v>13</v>
@@ -1891,38 +2371,38 @@
         <v>0.017</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F35" t="n">
-        <v>6.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45597</v>
+        <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C36" t="n">
         <v>0.17</v>
       </c>
       <c r="D36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F36" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45627</v>
+        <v>44896</v>
       </c>
       <c r="B37" t="n">
         <v>0</v>
@@ -1931,13 +2411,493 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="D37" t="n">
+        <v>19</v>
+      </c>
+      <c r="E37" t="n">
+        <v>11</v>
+      </c>
+      <c r="F37" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B40" t="n">
+        <v>15</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="D40" t="n">
+        <v>9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B41" t="n">
+        <v>15</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="D41" t="n">
+        <v>7</v>
+      </c>
+      <c r="E41" t="n">
+        <v>16</v>
+      </c>
+      <c r="F41" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B42" t="n">
+        <v>15</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="D42" t="n">
+        <v>6</v>
+      </c>
+      <c r="E42" t="n">
+        <v>15</v>
+      </c>
+      <c r="F42" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B43" t="n">
+        <v>15</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="n">
+        <v>13</v>
+      </c>
+      <c r="F43" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B44" t="n">
+        <v>15</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="D44" t="n">
+        <v>11</v>
+      </c>
+      <c r="E44" t="n">
+        <v>17</v>
+      </c>
+      <c r="F44" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B45" t="n">
+        <v>15</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="D45" t="n">
+        <v>17</v>
+      </c>
+      <c r="E45" t="n">
+        <v>17</v>
+      </c>
+      <c r="F45" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B46" t="n">
+        <v>14</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6</v>
+      </c>
+      <c r="E46" t="n">
+        <v>14</v>
+      </c>
+      <c r="F46" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B47" t="n">
+        <v>15</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="n">
+        <v>14</v>
+      </c>
+      <c r="F47" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B48" t="n">
+        <v>15</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="D48" t="n">
+        <v>14</v>
+      </c>
+      <c r="E48" t="n">
+        <v>15</v>
+      </c>
+      <c r="F48" t="n">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="D49" t="n">
+        <v>18</v>
+      </c>
+      <c r="E49" t="n">
+        <v>15</v>
+      </c>
+      <c r="F49" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B52" t="n">
+        <v>15</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="D52" t="n">
         <v>20</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="n">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B53" t="n">
+        <v>15</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="D53" t="n">
+        <v>15</v>
+      </c>
+      <c r="E53" t="n">
+        <v>14</v>
+      </c>
+      <c r="F53" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B54" t="n">
+        <v>15</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="D54" t="n">
+        <v>9</v>
+      </c>
+      <c r="E54" t="n">
+        <v>13</v>
+      </c>
+      <c r="F54" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B55" t="n">
+        <v>15</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>14</v>
+      </c>
+      <c r="F55" t="n">
+        <v>6.6</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B56" t="n">
+        <v>15</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="D56" t="n">
+        <v>20</v>
+      </c>
+      <c r="E56" t="n">
+        <v>15</v>
+      </c>
+      <c r="F56" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B57" t="n">
+        <v>15</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="D57" t="n">
+        <v>5</v>
+      </c>
+      <c r="E57" t="n">
+        <v>17</v>
+      </c>
+      <c r="F57" t="n">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B58" t="n">
+        <v>15</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="D58" t="n">
+        <v>20</v>
+      </c>
+      <c r="E58" t="n">
+        <v>14</v>
+      </c>
+      <c r="F58" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B59" t="n">
+        <v>15</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="D59" t="n">
+        <v>5</v>
+      </c>
+      <c r="E59" t="n">
+        <v>15</v>
+      </c>
+      <c r="F59" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B60" t="n">
+        <v>15</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D60" t="n">
+        <v>21</v>
+      </c>
+      <c r="E60" t="n">
+        <v>15</v>
+      </c>
+      <c r="F60" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="D61" t="n">
+        <v>19</v>
+      </c>
+      <c r="E61" t="n">
         <v>16</v>
       </c>
-      <c r="F37" t="n">
-        <v>7.3</v>
+      <c r="F61" t="n">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1951,7 +2911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1993,7 +2953,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44562</v>
+        <v>43831</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -2002,21 +2962,21 @@
         <v>0.19</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.132</v>
+        <v>0.199</v>
       </c>
       <c r="F2" t="n">
-        <v>0.174</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.283</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44593</v>
+        <v>43862</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -2025,21 +2985,21 @@
         <v>0.146</v>
       </c>
       <c r="D3" t="n">
-        <v>143</v>
+        <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>0.025</v>
+        <v>0.12</v>
       </c>
       <c r="F3" t="n">
-        <v>0.114</v>
+        <v>0.17</v>
       </c>
       <c r="G3" t="n">
-        <v>0.284</v>
+        <v>0.164</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44621</v>
+        <v>43891</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -2048,228 +3008,228 @@
         <v>0.217</v>
       </c>
       <c r="D4" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="E4" t="n">
-        <v>0.124</v>
+        <v>0.114</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.344</v>
       </c>
       <c r="G4" t="n">
-        <v>0.497</v>
+        <v>0.826</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44652</v>
+        <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C5" t="n">
         <v>0.294</v>
       </c>
       <c r="D5" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
-        <v>0.13</v>
+        <v>0.015</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="G5" t="n">
-        <v>0.317</v>
+        <v>0.828</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44682</v>
+        <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C6" t="n">
         <v>0.509</v>
       </c>
       <c r="D6" t="n">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E6" t="n">
-        <v>0.979</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.752</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44713</v>
+        <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
         <v>0.772</v>
       </c>
       <c r="D7" t="n">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="E7" t="n">
-        <v>0.843</v>
+        <v>0.746</v>
       </c>
       <c r="F7" t="n">
-        <v>0.318</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>0.424</v>
+        <v>0.9320000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44743</v>
+        <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="E8" t="n">
-        <v>0.958</v>
+        <v>0.921</v>
       </c>
       <c r="F8" t="n">
-        <v>0.407</v>
+        <v>0.331</v>
       </c>
       <c r="G8" t="n">
-        <v>0.958</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44774</v>
+        <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0.861</v>
       </c>
       <c r="D9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>0.926</v>
+        <v>0.631</v>
       </c>
       <c r="F9" t="n">
-        <v>0.576</v>
+        <v>0.258</v>
       </c>
       <c r="G9" t="n">
-        <v>0.968</v>
+        <v>0.879</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44805</v>
+        <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0.509</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="E10" t="n">
-        <v>0.719</v>
+        <v>0.384</v>
       </c>
       <c r="F10" t="n">
-        <v>0.786</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.246</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44835</v>
+        <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C11" t="n">
         <v>0.242</v>
       </c>
       <c r="D11" t="n">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="E11" t="n">
-        <v>0.285</v>
+        <v>0.096</v>
       </c>
       <c r="F11" t="n">
-        <v>0.912</v>
+        <v>0.831</v>
       </c>
       <c r="G11" t="n">
-        <v>0.279</v>
+        <v>0.131</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44866</v>
+        <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="C12" t="n">
         <v>0.163</v>
       </c>
       <c r="D12" t="n">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E12" t="n">
-        <v>0.304</v>
+        <v>0.058</v>
       </c>
       <c r="F12" t="n">
-        <v>0.043</v>
+        <v>0.037</v>
       </c>
       <c r="G12" t="n">
-        <v>0.312</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44896</v>
+        <v>44166</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="C13" t="n">
         <v>0.163</v>
       </c>
       <c r="D13" t="n">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="E13" t="n">
-        <v>0.225</v>
+        <v>0.196</v>
       </c>
       <c r="F13" t="n">
-        <v>0.054</v>
+        <v>0.131</v>
       </c>
       <c r="G13" t="n">
-        <v>0.118</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44927</v>
+        <v>44197</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -2278,21 +3238,21 @@
         <v>0.218</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.308</v>
+        <v>0.394</v>
       </c>
       <c r="F14" t="n">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.131</v>
+        <v>0.078</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44958</v>
+        <v>44228</v>
       </c>
       <c r="B15" t="n">
         <v>0</v>
@@ -2301,21 +3261,21 @@
         <v>0.043</v>
       </c>
       <c r="D15" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E15" t="n">
-        <v>0.198</v>
+        <v>0.097</v>
       </c>
       <c r="F15" t="n">
-        <v>0.075</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.033</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44986</v>
+        <v>44256</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -2324,228 +3284,228 @@
         <v>0.055</v>
       </c>
       <c r="D16" t="n">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="E16" t="n">
-        <v>0.209</v>
+        <v>0.269</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="G16" t="n">
-        <v>0.975</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45017</v>
+        <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C17" t="n">
         <v>0.144</v>
       </c>
       <c r="D17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E17" t="n">
-        <v>0.171</v>
+        <v>0.305</v>
       </c>
       <c r="F17" t="n">
-        <v>0.154</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.897</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45047</v>
+        <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C18" t="n">
         <v>0.453</v>
       </c>
       <c r="D18" t="n">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="E18" t="n">
-        <v>0.88</v>
+        <v>0.318</v>
       </c>
       <c r="F18" t="n">
-        <v>0.004</v>
+        <v>0.269</v>
       </c>
       <c r="G18" t="n">
-        <v>0.506</v>
+        <v>0.965</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45078</v>
+        <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C19" t="n">
         <v>0.8090000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E19" t="n">
-        <v>0.55</v>
+        <v>0.376</v>
       </c>
       <c r="F19" t="n">
-        <v>0.537</v>
+        <v>0.736</v>
       </c>
       <c r="G19" t="n">
-        <v>0.57</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45108</v>
+        <v>44378</v>
       </c>
       <c r="B20" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0.799</v>
       </c>
       <c r="D20" t="n">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="E20" t="n">
-        <v>0.497</v>
+        <v>0.322</v>
       </c>
       <c r="F20" t="n">
-        <v>0.731</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>0.896</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45139</v>
+        <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>0.658</v>
       </c>
       <c r="D21" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>0.68</v>
+        <v>0.745</v>
       </c>
       <c r="F21" t="n">
-        <v>0.68</v>
+        <v>0.668</v>
       </c>
       <c r="G21" t="n">
-        <v>0.522</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45170</v>
+        <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0.624</v>
       </c>
       <c r="D22" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E22" t="n">
-        <v>0.399</v>
+        <v>0.52</v>
       </c>
       <c r="F22" t="n">
-        <v>0.587</v>
+        <v>0.419</v>
       </c>
       <c r="G22" t="n">
-        <v>0.011</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45200</v>
+        <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C23" t="n">
         <v>0.132</v>
       </c>
       <c r="D23" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="E23" t="n">
-        <v>0.203</v>
+        <v>0.214</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0.351</v>
       </c>
       <c r="G23" t="n">
-        <v>0.013</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45231</v>
+        <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="C24" t="n">
         <v>0.148</v>
       </c>
       <c r="D24" t="n">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="E24" t="n">
-        <v>0.363</v>
+        <v>0.036</v>
       </c>
       <c r="F24" t="n">
-        <v>0.186</v>
+        <v>0.203</v>
       </c>
       <c r="G24" t="n">
-        <v>0.288</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45261</v>
+        <v>44531</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="C25" t="n">
         <v>0.021</v>
       </c>
       <c r="D25" t="n">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1</v>
+        <v>0.334</v>
       </c>
       <c r="F25" t="n">
-        <v>0.248</v>
+        <v>0.006</v>
       </c>
       <c r="G25" t="n">
-        <v>0.126</v>
+        <v>0.183</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45292</v>
+        <v>44562</v>
       </c>
       <c r="B26" t="n">
         <v>0</v>
@@ -2554,21 +3514,21 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>0.164</v>
+        <v>0.128</v>
       </c>
       <c r="F26" t="n">
-        <v>0.116</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.044</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45323</v>
+        <v>44593</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -2577,21 +3537,21 @@
         <v>0.13</v>
       </c>
       <c r="D27" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E27" t="n">
-        <v>0.302</v>
+        <v>0.075</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.128</v>
       </c>
       <c r="G27" t="n">
-        <v>0.183</v>
+        <v>0.244</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45352</v>
+        <v>44621</v>
       </c>
       <c r="B28" t="n">
         <v>0</v>
@@ -2600,223 +3560,775 @@
         <v>0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="E28" t="n">
-        <v>0.092</v>
+        <v>0.016</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.063</v>
       </c>
       <c r="G28" t="n">
-        <v>0.731</v>
+        <v>0.364</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45383</v>
+        <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="C29" t="n">
         <v>0.141</v>
       </c>
       <c r="D29" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>0.031</v>
+        <v>0.236</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="G29" t="n">
-        <v>0.993</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45413</v>
+        <v>44682</v>
       </c>
       <c r="B30" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C30" t="n">
         <v>0.408</v>
       </c>
       <c r="D30" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="E30" t="n">
-        <v>0.795</v>
+        <v>0.503</v>
       </c>
       <c r="F30" t="n">
-        <v>0.131</v>
+        <v>0.012</v>
       </c>
       <c r="G30" t="n">
-        <v>0.398</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45444</v>
+        <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C31" t="n">
         <v>0.6860000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.413</v>
       </c>
       <c r="F31" t="n">
-        <v>0.636</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>0.663</v>
+        <v>0.6850000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45474</v>
+        <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
         <v>0.753</v>
       </c>
       <c r="D32" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E32" t="n">
-        <v>0.84</v>
+        <v>0.951</v>
       </c>
       <c r="F32" t="n">
-        <v>0.269</v>
+        <v>0.673</v>
       </c>
       <c r="G32" t="n">
-        <v>0.914</v>
+        <v>0.609</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45505</v>
+        <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
         <v>0.854</v>
       </c>
       <c r="D33" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E33" t="n">
-        <v>0.352</v>
+        <v>0.866</v>
       </c>
       <c r="F33" t="n">
-        <v>0.506</v>
+        <v>0.66</v>
       </c>
       <c r="G33" t="n">
-        <v>0.819</v>
+        <v>0.921</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45536</v>
+        <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>0.449</v>
       </c>
       <c r="D34" t="n">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="E34" t="n">
-        <v>0.551</v>
+        <v>0.743</v>
       </c>
       <c r="F34" t="n">
-        <v>0.928</v>
+        <v>0.515</v>
       </c>
       <c r="G34" t="n">
-        <v>0.189</v>
+        <v>0.333</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45566</v>
+        <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C35" t="n">
         <v>0.017</v>
       </c>
       <c r="D35" t="n">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="E35" t="n">
-        <v>0.349</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.537</v>
+        <v>0.654</v>
       </c>
       <c r="G35" t="n">
-        <v>0.223</v>
+        <v>0.312</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45597</v>
+        <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="C36" t="n">
         <v>0.17</v>
       </c>
       <c r="D36" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="E36" t="n">
-        <v>0.321</v>
+        <v>0.276</v>
       </c>
       <c r="F36" t="n">
-        <v>0.053</v>
+        <v>0.329</v>
       </c>
       <c r="G36" t="n">
-        <v>0.254</v>
+        <v>0.159</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45627</v>
+        <v>44896</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="C37" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>116</v>
+        <v>57</v>
       </c>
       <c r="E37" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.217</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="D38" t="n">
+        <v>11</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.097</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>102</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.066</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="D40" t="n">
+        <v>84</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.359</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B41" t="n">
+        <v>90</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="D41" t="n">
+        <v>21</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.791</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B42" t="n">
+        <v>96</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="D42" t="n">
+        <v>93</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.351</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B43" t="n">
+        <v>89</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="D43" t="n">
+        <v>75</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.842</v>
+      </c>
+      <c r="D44" t="n">
+        <v>112</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.794</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="D45" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.357</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="D46" t="n">
+        <v>67</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.244</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B47" t="n">
+        <v>83</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="D47" t="n">
+        <v>67</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.188</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B48" t="n">
+        <v>100</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="D48" t="n">
+        <v>54</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.108</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="D49" t="n">
+        <v>124</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.285</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B50" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="D50" t="n">
+        <v>24</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="D51" t="n">
+        <v>97</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="F51" t="n">
         <v>0.075</v>
       </c>
-      <c r="F37" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0.342</v>
+      <c r="G51" t="n">
+        <v>0.057</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="D52" t="n">
+        <v>134</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="D53" t="n">
+        <v>14</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.827</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B54" t="n">
+        <v>93</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="D54" t="n">
+        <v>109</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B55" t="n">
+        <v>86</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="D55" t="n">
+        <v>137</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.358</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="D56" t="n">
+        <v>71</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.844</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="D57" t="n">
+        <v>19</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="D58" t="n">
+        <v>77</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.326</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B59" t="n">
+        <v>91</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0.164</v>
+      </c>
+      <c r="D59" t="n">
+        <v>56</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.303</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B60" t="n">
+        <v>92</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="D60" t="n">
+        <v>103</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B61" t="n">
+        <v>91</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="D61" t="n">
+        <v>144</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.008999999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/data/data.xlsx
+++ b/inputs/data/data.xlsx
@@ -1711,13 +1711,13 @@
         <v>0.19</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1737,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4">
@@ -1745,19 +1745,19 @@
         <v>43891</v>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>0.217</v>
       </c>
       <c r="D4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -1765,19 +1765,19 @@
         <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
         <v>0.294</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>9.6</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1785,19 +1785,19 @@
         <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
         <v>0.509</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="7">
@@ -1805,7 +1805,7 @@
         <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
         <v>0.772</v>
@@ -1814,10 +1814,10 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>9.9</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="8">
@@ -1825,19 +1825,19 @@
         <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F8" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="9">
@@ -1845,19 +1845,19 @@
         <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
         <v>0.861</v>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="10">
@@ -1865,7 +1865,7 @@
         <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
         <v>0.509</v>
@@ -1874,10 +1874,10 @@
         <v>20</v>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="n">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="11">
@@ -1885,19 +1885,19 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>0.242</v>
       </c>
       <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" t="n">
         <v>6</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" t="n">
-        <v>8.1</v>
       </c>
     </row>
     <row r="12">
@@ -1905,19 +1905,19 @@
         <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
         <v>0.163</v>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1931,13 +1931,13 @@
         <v>0.163</v>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
         <v>9</v>
       </c>
       <c r="F13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1951,13 +1951,13 @@
         <v>0.218</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="15">
@@ -1971,13 +1971,13 @@
         <v>0.043</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>9.300000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -1991,13 +1991,13 @@
         <v>0.055</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="17">
@@ -2005,19 +2005,19 @@
         <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
         <v>0.144</v>
       </c>
       <c r="D17" t="n">
+        <v>9</v>
+      </c>
+      <c r="E17" t="n">
         <v>13</v>
       </c>
-      <c r="E17" t="n">
-        <v>14</v>
-      </c>
       <c r="F17" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -2025,19 +2025,19 @@
         <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
         <v>0.453</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -2045,19 +2045,19 @@
         <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
         <v>0.8090000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F19" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="20">
@@ -2065,19 +2065,19 @@
         <v>44378</v>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
         <v>0.799</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2085,19 +2085,19 @@
         <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
         <v>0.658</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>6.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -2105,7 +2105,7 @@
         <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C22" t="n">
         <v>0.624</v>
@@ -2114,10 +2114,10 @@
         <v>17</v>
       </c>
       <c r="E22" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="23">
@@ -2125,7 +2125,7 @@
         <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
         <v>0.132</v>
@@ -2134,10 +2134,10 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F23" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="24">
@@ -2145,19 +2145,19 @@
         <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C24" t="n">
         <v>0.148</v>
       </c>
       <c r="D24" t="n">
+        <v>19</v>
+      </c>
+      <c r="E24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
-        <v>10</v>
-      </c>
       <c r="F24" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="25">
@@ -2171,13 +2171,13 @@
         <v>0.021</v>
       </c>
       <c r="D25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>8.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -2191,13 +2191,13 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="27">
@@ -2211,13 +2211,13 @@
         <v>0.13</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="28">
@@ -2225,19 +2225,19 @@
         <v>44621</v>
       </c>
       <c r="B28" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C28" t="n">
         <v>0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="29">
@@ -2245,19 +2245,19 @@
         <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C29" t="n">
         <v>0.141</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="30">
@@ -2265,19 +2265,19 @@
         <v>44682</v>
       </c>
       <c r="B30" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C30" t="n">
         <v>0.408</v>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E30" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F30" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -2285,19 +2285,19 @@
         <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C31" t="n">
         <v>0.6860000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="32">
@@ -2305,19 +2305,19 @@
         <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C32" t="n">
         <v>0.753</v>
       </c>
       <c r="D32" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F32" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="33">
@@ -2331,13 +2331,13 @@
         <v>0.854</v>
       </c>
       <c r="D33" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E33" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F33" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="34">
@@ -2345,19 +2345,19 @@
         <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C34" t="n">
         <v>0.449</v>
       </c>
       <c r="D34" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E34" t="n">
         <v>12</v>
       </c>
       <c r="F34" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="35">
@@ -2365,19 +2365,19 @@
         <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C35" t="n">
         <v>0.017</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F35" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="36">
@@ -2385,19 +2385,19 @@
         <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
         <v>0.17</v>
       </c>
       <c r="D36" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E36" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F36" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="37">
@@ -2411,13 +2411,13 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F37" t="n">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="38">
@@ -2431,13 +2431,13 @@
         <v>0.128</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="39">
@@ -2451,13 +2451,13 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -2471,13 +2471,13 @@
         <v>0.016</v>
       </c>
       <c r="D40" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="41">
@@ -2485,19 +2485,19 @@
         <v>45017</v>
       </c>
       <c r="B41" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C41" t="n">
         <v>0.145</v>
       </c>
       <c r="D41" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E41" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F41" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -2505,19 +2505,19 @@
         <v>45047</v>
       </c>
       <c r="B42" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C42" t="n">
         <v>0.545</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E42" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F42" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="43">
@@ -2525,19 +2525,19 @@
         <v>45078</v>
       </c>
       <c r="B43" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C43" t="n">
         <v>0.763</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
         <v>13</v>
       </c>
       <c r="F43" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -2551,13 +2551,13 @@
         <v>0.842</v>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E44" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F44" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="45">
@@ -2565,19 +2565,19 @@
         <v>45139</v>
       </c>
       <c r="B45" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C45" t="n">
         <v>0.74</v>
       </c>
       <c r="D45" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E45" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F45" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="46">
@@ -2585,19 +2585,19 @@
         <v>45170</v>
       </c>
       <c r="B46" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C46" t="n">
         <v>0.397</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E46" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F46" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -2605,19 +2605,19 @@
         <v>45200</v>
       </c>
       <c r="B47" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C47" t="n">
         <v>0.115</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="48">
@@ -2625,19 +2625,19 @@
         <v>45231</v>
       </c>
       <c r="B48" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C48" t="n">
         <v>0.142</v>
       </c>
       <c r="D48" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E48" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F48" t="n">
-        <v>6.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2651,13 +2651,13 @@
         <v>0.269</v>
       </c>
       <c r="D49" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E49" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F49" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="50">
@@ -2671,13 +2671,13 @@
         <v>0.217</v>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>9.300000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="51">
@@ -2691,13 +2691,13 @@
         <v>0.053</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52">
@@ -2705,19 +2705,19 @@
         <v>45352</v>
       </c>
       <c r="B52" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C52" t="n">
         <v>0.223</v>
       </c>
       <c r="D52" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="53">
@@ -2725,19 +2725,19 @@
         <v>45383</v>
       </c>
       <c r="B53" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C53" t="n">
         <v>0.168</v>
       </c>
       <c r="D53" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E53" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F53" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="54">
@@ -2745,19 +2745,19 @@
         <v>45413</v>
       </c>
       <c r="B54" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C54" t="n">
         <v>0.496</v>
       </c>
       <c r="D54" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E54" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F54" t="n">
-        <v>7.5</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="55">
@@ -2765,19 +2765,19 @@
         <v>45444</v>
       </c>
       <c r="B55" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C55" t="n">
         <v>0.855</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E55" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F55" t="n">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="56">
@@ -2791,13 +2791,13 @@
         <v>0.981</v>
       </c>
       <c r="D56" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E56" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -2805,19 +2805,19 @@
         <v>45505</v>
       </c>
       <c r="B57" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C57" t="n">
         <v>0.877</v>
       </c>
       <c r="D57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E57" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F57" t="n">
-        <v>7.2</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="58">
@@ -2825,19 +2825,19 @@
         <v>45536</v>
       </c>
       <c r="B58" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C58" t="n">
         <v>0.476</v>
       </c>
       <c r="D58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E58" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F58" t="n">
-        <v>6.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2851,13 +2851,13 @@
         <v>0.164</v>
       </c>
       <c r="D59" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F59" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="60">
@@ -2865,19 +2865,19 @@
         <v>45597</v>
       </c>
       <c r="B60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C60" t="n">
         <v>0.21</v>
       </c>
       <c r="D60" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E60" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F60" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="61">
@@ -2891,13 +2891,13 @@
         <v>0.255</v>
       </c>
       <c r="D61" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E61" t="n">
         <v>16</v>
       </c>
       <c r="F61" t="n">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -2962,7 +2962,7 @@
         <v>0.19</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.199</v>
@@ -2985,7 +2985,7 @@
         <v>0.146</v>
       </c>
       <c r="D3" t="n">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="E3" t="n">
         <v>0.12</v>
@@ -3008,7 +3008,7 @@
         <v>0.217</v>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="E4" t="n">
         <v>0.114</v>
@@ -3025,13 +3025,13 @@
         <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C5" t="n">
         <v>0.294</v>
       </c>
       <c r="D5" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
         <v>0.015</v>
@@ -3048,13 +3048,13 @@
         <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C6" t="n">
         <v>0.509</v>
       </c>
       <c r="D6" t="n">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="E6" t="n">
         <v>0.8110000000000001</v>
@@ -3071,13 +3071,13 @@
         <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
         <v>0.772</v>
       </c>
       <c r="D7" t="n">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="E7" t="n">
         <v>0.746</v>
@@ -3094,13 +3094,13 @@
         <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="E8" t="n">
         <v>0.921</v>
@@ -3117,13 +3117,13 @@
         <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C9" t="n">
         <v>0.861</v>
       </c>
       <c r="D9" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0.631</v>
@@ -3140,13 +3140,13 @@
         <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C10" t="n">
         <v>0.509</v>
       </c>
       <c r="D10" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E10" t="n">
         <v>0.384</v>
@@ -3163,13 +3163,13 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C11" t="n">
         <v>0.242</v>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="E11" t="n">
         <v>0.096</v>
@@ -3192,7 +3192,7 @@
         <v>0.163</v>
       </c>
       <c r="D12" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E12" t="n">
         <v>0.058</v>
@@ -3215,7 +3215,7 @@
         <v>0.163</v>
       </c>
       <c r="D13" t="n">
-        <v>141</v>
+        <v>62</v>
       </c>
       <c r="E13" t="n">
         <v>0.196</v>
@@ -3238,7 +3238,7 @@
         <v>0.218</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E14" t="n">
         <v>0.394</v>
@@ -3261,7 +3261,7 @@
         <v>0.043</v>
       </c>
       <c r="D15" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="E15" t="n">
         <v>0.097</v>
@@ -3284,7 +3284,7 @@
         <v>0.055</v>
       </c>
       <c r="D16" t="n">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="E16" t="n">
         <v>0.269</v>
@@ -3301,13 +3301,13 @@
         <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C17" t="n">
         <v>0.144</v>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E17" t="n">
         <v>0.305</v>
@@ -3324,13 +3324,13 @@
         <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C18" t="n">
         <v>0.453</v>
       </c>
       <c r="D18" t="n">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="E18" t="n">
         <v>0.318</v>
@@ -3347,13 +3347,13 @@
         <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C19" t="n">
         <v>0.8090000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="E19" t="n">
         <v>0.376</v>
@@ -3376,7 +3376,7 @@
         <v>0.799</v>
       </c>
       <c r="D20" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E20" t="n">
         <v>0.322</v>
@@ -3393,13 +3393,13 @@
         <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C21" t="n">
         <v>0.658</v>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
         <v>0.745</v>
@@ -3416,13 +3416,13 @@
         <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C22" t="n">
         <v>0.624</v>
       </c>
       <c r="D22" t="n">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="E22" t="n">
         <v>0.52</v>
@@ -3445,7 +3445,7 @@
         <v>0.132</v>
       </c>
       <c r="D23" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E23" t="n">
         <v>0.214</v>
@@ -3468,7 +3468,7 @@
         <v>0.148</v>
       </c>
       <c r="D24" t="n">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="E24" t="n">
         <v>0.036</v>
@@ -3491,7 +3491,7 @@
         <v>0.021</v>
       </c>
       <c r="D25" t="n">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="E25" t="n">
         <v>0.334</v>
@@ -3514,7 +3514,7 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
         <v>0.128</v>
@@ -3537,7 +3537,7 @@
         <v>0.13</v>
       </c>
       <c r="D27" t="n">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="E27" t="n">
         <v>0.075</v>
@@ -3560,7 +3560,7 @@
         <v>0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="E28" t="n">
         <v>0.016</v>
@@ -3577,13 +3577,13 @@
         <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C29" t="n">
         <v>0.141</v>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E29" t="n">
         <v>0.236</v>
@@ -3606,7 +3606,7 @@
         <v>0.408</v>
       </c>
       <c r="D30" t="n">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="E30" t="n">
         <v>0.503</v>
@@ -3623,13 +3623,13 @@
         <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C31" t="n">
         <v>0.6860000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="E31" t="n">
         <v>0.413</v>
@@ -3646,13 +3646,13 @@
         <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C32" t="n">
         <v>0.753</v>
       </c>
       <c r="D32" t="n">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="E32" t="n">
         <v>0.951</v>
@@ -3669,13 +3669,13 @@
         <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C33" t="n">
         <v>0.854</v>
       </c>
       <c r="D33" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E33" t="n">
         <v>0.866</v>
@@ -3698,7 +3698,7 @@
         <v>0.449</v>
       </c>
       <c r="D34" t="n">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="E34" t="n">
         <v>0.743</v>
@@ -3715,13 +3715,13 @@
         <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C35" t="n">
         <v>0.017</v>
       </c>
       <c r="D35" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E35" t="n">
         <v>0.07000000000000001</v>
@@ -3744,7 +3744,7 @@
         <v>0.17</v>
       </c>
       <c r="D36" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="E36" t="n">
         <v>0.276</v>
@@ -3767,7 +3767,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="E37" t="n">
         <v>0.155</v>
@@ -3790,7 +3790,7 @@
         <v>0.128</v>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E38" t="n">
         <v>0.375</v>
@@ -3813,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E39" t="n">
         <v>0.055</v>
@@ -3836,7 +3836,7 @@
         <v>0.016</v>
       </c>
       <c r="D40" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="E40" t="n">
         <v>0.136</v>
@@ -3853,13 +3853,13 @@
         <v>45017</v>
       </c>
       <c r="B41" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C41" t="n">
         <v>0.145</v>
       </c>
       <c r="D41" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E41" t="n">
         <v>0.045</v>
@@ -3876,13 +3876,13 @@
         <v>45047</v>
       </c>
       <c r="B42" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C42" t="n">
         <v>0.545</v>
       </c>
       <c r="D42" t="n">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="E42" t="n">
         <v>0.523</v>
@@ -3899,13 +3899,13 @@
         <v>45078</v>
       </c>
       <c r="B43" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C43" t="n">
         <v>0.763</v>
       </c>
       <c r="D43" t="n">
-        <v>75</v>
+        <v>122</v>
       </c>
       <c r="E43" t="n">
         <v>0.377</v>
@@ -3922,13 +3922,13 @@
         <v>45108</v>
       </c>
       <c r="B44" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C44" t="n">
         <v>0.842</v>
       </c>
       <c r="D44" t="n">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="E44" t="n">
         <v>0.46</v>
@@ -3945,13 +3945,13 @@
         <v>45139</v>
       </c>
       <c r="B45" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C45" t="n">
         <v>0.74</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E45" t="n">
         <v>0.599</v>
@@ -3974,7 +3974,7 @@
         <v>0.397</v>
       </c>
       <c r="D46" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E46" t="n">
         <v>0.873</v>
@@ -3991,13 +3991,13 @@
         <v>45200</v>
       </c>
       <c r="B47" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C47" t="n">
         <v>0.115</v>
       </c>
       <c r="D47" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E47" t="n">
         <v>0.222</v>
@@ -4020,7 +4020,7 @@
         <v>0.142</v>
       </c>
       <c r="D48" t="n">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="E48" t="n">
         <v>0.212</v>
@@ -4043,7 +4043,7 @@
         <v>0.269</v>
       </c>
       <c r="D49" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="E49" t="n">
         <v>0.097</v>
@@ -4066,7 +4066,7 @@
         <v>0.217</v>
       </c>
       <c r="D50" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E50" t="n">
         <v>0.037</v>
@@ -4089,7 +4089,7 @@
         <v>0.053</v>
       </c>
       <c r="D51" t="n">
-        <v>97</v>
+        <v>143</v>
       </c>
       <c r="E51" t="n">
         <v>0.359</v>
@@ -4112,7 +4112,7 @@
         <v>0.223</v>
       </c>
       <c r="D52" t="n">
-        <v>134</v>
+        <v>56</v>
       </c>
       <c r="E52" t="n">
         <v>0.36</v>
@@ -4129,13 +4129,13 @@
         <v>45383</v>
       </c>
       <c r="B53" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C53" t="n">
         <v>0.168</v>
       </c>
       <c r="D53" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E53" t="n">
         <v>0.253</v>
@@ -4158,7 +4158,7 @@
         <v>0.496</v>
       </c>
       <c r="D54" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="E54" t="n">
         <v>0.96</v>
@@ -4175,13 +4175,13 @@
         <v>45444</v>
       </c>
       <c r="B55" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C55" t="n">
         <v>0.855</v>
       </c>
       <c r="D55" t="n">
-        <v>137</v>
+        <v>60</v>
       </c>
       <c r="E55" t="n">
         <v>0.526</v>
@@ -4198,13 +4198,13 @@
         <v>45474</v>
       </c>
       <c r="B56" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C56" t="n">
         <v>0.981</v>
       </c>
       <c r="D56" t="n">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="E56" t="n">
         <v>0.663</v>
@@ -4221,13 +4221,13 @@
         <v>45505</v>
       </c>
       <c r="B57" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C57" t="n">
         <v>0.877</v>
       </c>
       <c r="D57" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E57" t="n">
         <v>0.792</v>
@@ -4244,13 +4244,13 @@
         <v>45536</v>
       </c>
       <c r="B58" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C58" t="n">
         <v>0.476</v>
       </c>
       <c r="D58" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E58" t="n">
         <v>0.555</v>
@@ -4267,13 +4267,13 @@
         <v>45566</v>
       </c>
       <c r="B59" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C59" t="n">
         <v>0.164</v>
       </c>
       <c r="D59" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="E59" t="n">
         <v>0.312</v>
@@ -4296,7 +4296,7 @@
         <v>0.21</v>
       </c>
       <c r="D60" t="n">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="E60" t="n">
         <v>0.257</v>
@@ -4319,7 +4319,7 @@
         <v>0.255</v>
       </c>
       <c r="D61" t="n">
-        <v>144</v>
+        <v>104</v>
       </c>
       <c r="E61" t="n">
         <v>0.034</v>

--- a/inputs/data/data.xlsx
+++ b/inputs/data/data.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="10KV电缆" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="柱上变压器台成套设备" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="10kv交流避雷器" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10KV电缆" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="柱上变压器台成套设备" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10kv交流避雷器" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -459,19 +459,19 @@
         <v>43831</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
         <v>0.19</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="3">
@@ -479,19 +479,19 @@
         <v>43862</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
         <v>0.146</v>
       </c>
       <c r="D3" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4">
@@ -499,19 +499,19 @@
         <v>43891</v>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>0.217</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
@@ -519,19 +519,19 @@
         <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>0.294</v>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="6">
@@ -539,19 +539,19 @@
         <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
         <v>0.509</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F6" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="7">
@@ -559,19 +559,19 @@
         <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
         <v>0.772</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="8">
@@ -579,19 +579,19 @@
         <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="9">
@@ -599,19 +599,19 @@
         <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
         <v>0.861</v>
       </c>
       <c r="D9" t="n">
+        <v>17</v>
+      </c>
+      <c r="E9" t="n">
         <v>14</v>
       </c>
-      <c r="E9" t="n">
-        <v>15</v>
-      </c>
       <c r="F9" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="10">
@@ -619,19 +619,19 @@
         <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>0.509</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="11">
@@ -639,19 +639,19 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
         <v>0.242</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="12">
@@ -659,19 +659,19 @@
         <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
         <v>0.163</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -685,10 +685,10 @@
         <v>0.163</v>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>4.3</v>
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="15">
@@ -719,19 +719,19 @@
         <v>44228</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>0.043</v>
       </c>
       <c r="D15" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="16">
@@ -739,19 +739,19 @@
         <v>44256</v>
       </c>
       <c r="B16" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>0.055</v>
       </c>
       <c r="D16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="17">
@@ -759,19 +759,19 @@
         <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
         <v>0.144</v>
       </c>
       <c r="D17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F17" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -779,19 +779,19 @@
         <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>0.453</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="19">
@@ -799,19 +799,19 @@
         <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
         <v>0.8090000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="F19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="20">
@@ -819,19 +819,19 @@
         <v>44378</v>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
         <v>0.799</v>
       </c>
       <c r="D20" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F20" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="21">
@@ -839,19 +839,19 @@
         <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C21" t="n">
         <v>0.658</v>
       </c>
       <c r="D21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="22">
@@ -859,19 +859,19 @@
         <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
         <v>0.624</v>
       </c>
       <c r="D22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F22" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="23">
@@ -879,19 +879,19 @@
         <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
         <v>0.132</v>
       </c>
       <c r="D23" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -899,19 +899,19 @@
         <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
         <v>0.148</v>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="25">
@@ -925,13 +925,13 @@
         <v>0.021</v>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="26">
@@ -945,13 +945,13 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>4.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="27">
@@ -959,19 +959,19 @@
         <v>44593</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C27" t="n">
         <v>0.13</v>
       </c>
       <c r="D27" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="28">
@@ -979,19 +979,19 @@
         <v>44621</v>
       </c>
       <c r="B28" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C28" t="n">
         <v>0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F28" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="29">
@@ -999,19 +999,19 @@
         <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C29" t="n">
         <v>0.141</v>
       </c>
       <c r="D29" t="n">
+        <v>13</v>
+      </c>
+      <c r="E29" t="n">
         <v>21</v>
       </c>
-      <c r="E29" t="n">
-        <v>25</v>
-      </c>
       <c r="F29" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="30">
@@ -1019,19 +1019,19 @@
         <v>44682</v>
       </c>
       <c r="B30" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C30" t="n">
         <v>0.408</v>
       </c>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="31">
@@ -1039,19 +1039,19 @@
         <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C31" t="n">
         <v>0.6860000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F31" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -1059,19 +1059,19 @@
         <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C32" t="n">
         <v>0.753</v>
       </c>
       <c r="D32" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E32" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="33">
@@ -1079,19 +1079,19 @@
         <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C33" t="n">
         <v>0.854</v>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E33" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F33" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="34">
@@ -1099,19 +1099,19 @@
         <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C34" t="n">
         <v>0.449</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="F34" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="35">
@@ -1119,19 +1119,19 @@
         <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C35" t="n">
         <v>0.017</v>
       </c>
       <c r="D35" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E35" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F35" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -1139,19 +1139,19 @@
         <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C36" t="n">
         <v>0.17</v>
       </c>
       <c r="D36" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E36" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F36" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="37">
@@ -1159,19 +1159,19 @@
         <v>44896</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E37" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F37" t="n">
-        <v>2.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="38">
@@ -1185,13 +1185,13 @@
         <v>0.128</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F38" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="39">
@@ -1205,13 +1205,13 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="40">
@@ -1219,19 +1219,19 @@
         <v>44986</v>
       </c>
       <c r="B40" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C40" t="n">
         <v>0.016</v>
       </c>
       <c r="D40" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="41">
@@ -1245,13 +1245,13 @@
         <v>0.145</v>
       </c>
       <c r="D41" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E41" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F41" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -1259,19 +1259,19 @@
         <v>45047</v>
       </c>
       <c r="B42" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C42" t="n">
         <v>0.545</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F42" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="43">
@@ -1279,19 +1279,19 @@
         <v>45078</v>
       </c>
       <c r="B43" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="C43" t="n">
         <v>0.763</v>
       </c>
       <c r="D43" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E43" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F43" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -1299,19 +1299,19 @@
         <v>45108</v>
       </c>
       <c r="B44" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C44" t="n">
         <v>0.842</v>
       </c>
       <c r="D44" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E44" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F44" t="n">
-        <v>6.7</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="45">
@@ -1319,19 +1319,19 @@
         <v>45139</v>
       </c>
       <c r="B45" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C45" t="n">
         <v>0.74</v>
       </c>
       <c r="D45" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E45" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="F45" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="46">
@@ -1339,19 +1339,19 @@
         <v>45170</v>
       </c>
       <c r="B46" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C46" t="n">
         <v>0.397</v>
       </c>
       <c r="D46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F46" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="47">
@@ -1359,19 +1359,19 @@
         <v>45200</v>
       </c>
       <c r="B47" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C47" t="n">
         <v>0.115</v>
       </c>
       <c r="D47" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E47" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F47" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="48">
@@ -1379,19 +1379,19 @@
         <v>45231</v>
       </c>
       <c r="B48" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
         <v>0.142</v>
       </c>
       <c r="D48" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E48" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F48" t="n">
-        <v>6.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="49">
@@ -1399,19 +1399,19 @@
         <v>45261</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C49" t="n">
         <v>0.269</v>
       </c>
       <c r="D49" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E49" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -1419,19 +1419,19 @@
         <v>45292</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C50" t="n">
         <v>0.217</v>
       </c>
       <c r="D50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F50" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="51">
@@ -1439,19 +1439,19 @@
         <v>45323</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C51" t="n">
         <v>0.053</v>
       </c>
       <c r="D51" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="52">
@@ -1459,19 +1459,19 @@
         <v>45352</v>
       </c>
       <c r="B52" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C52" t="n">
         <v>0.223</v>
       </c>
       <c r="D52" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F52" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="53">
@@ -1485,13 +1485,13 @@
         <v>0.168</v>
       </c>
       <c r="D53" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E53" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F53" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="54">
@@ -1499,19 +1499,19 @@
         <v>45413</v>
       </c>
       <c r="B54" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C54" t="n">
         <v>0.496</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E54" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F54" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="55">
@@ -1519,19 +1519,19 @@
         <v>45444</v>
       </c>
       <c r="B55" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C55" t="n">
         <v>0.855</v>
       </c>
       <c r="D55" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E55" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F55" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="56">
@@ -1539,19 +1539,19 @@
         <v>45474</v>
       </c>
       <c r="B56" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C56" t="n">
         <v>0.981</v>
       </c>
       <c r="D56" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E56" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F56" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="57">
@@ -1559,19 +1559,19 @@
         <v>45505</v>
       </c>
       <c r="B57" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C57" t="n">
         <v>0.877</v>
       </c>
       <c r="D57" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E57" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F57" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="58">
@@ -1579,7 +1579,7 @@
         <v>45536</v>
       </c>
       <c r="B58" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C58" t="n">
         <v>0.476</v>
@@ -1588,10 +1588,10 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F58" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="59">
@@ -1599,19 +1599,19 @@
         <v>45566</v>
       </c>
       <c r="B59" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="C59" t="n">
         <v>0.164</v>
       </c>
       <c r="D59" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E59" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F59" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -1619,19 +1619,19 @@
         <v>45597</v>
       </c>
       <c r="B60" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C60" t="n">
         <v>0.21</v>
       </c>
       <c r="D60" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E60" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="F60" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="61">
@@ -1645,13 +1645,13 @@
         <v>0.255</v>
       </c>
       <c r="D61" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E61" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F61" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3">
@@ -1731,13 +1731,13 @@
         <v>0.146</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4">
@@ -1745,19 +1745,19 @@
         <v>43891</v>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
         <v>0.217</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1765,19 +1765,19 @@
         <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
         <v>0.294</v>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="6">
@@ -1785,19 +1785,19 @@
         <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
         <v>0.509</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -1811,13 +1811,13 @@
         <v>0.772</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="8">
@@ -1825,19 +1825,19 @@
         <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
@@ -1845,19 +1845,19 @@
         <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
         <v>0.861</v>
       </c>
       <c r="D9" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10">
@@ -1865,19 +1865,19 @@
         <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
         <v>0.509</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F10" t="n">
-        <v>6.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1885,7 +1885,7 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0.242</v>
@@ -1894,10 +1894,10 @@
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="12">
@@ -1905,19 +1905,19 @@
         <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
         <v>0.163</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="13">
@@ -1931,13 +1931,13 @@
         <v>0.163</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" t="n">
         <v>9</v>
-      </c>
-      <c r="F13" t="n">
-        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="15">
@@ -1965,19 +1965,19 @@
         <v>44228</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
         <v>0.043</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1985,19 +1985,19 @@
         <v>44256</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>0.055</v>
       </c>
       <c r="D16" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" t="n">
         <v>11</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
       <c r="F16" t="n">
-        <v>7.9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -2005,19 +2005,19 @@
         <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
         <v>0.144</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="18">
@@ -2025,19 +2025,19 @@
         <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
         <v>0.453</v>
       </c>
       <c r="D18" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F18" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -2045,19 +2045,19 @@
         <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
         <v>0.8090000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -2065,7 +2065,7 @@
         <v>44378</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
         <v>0.799</v>
@@ -2074,10 +2074,10 @@
         <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="21">
@@ -2085,19 +2085,19 @@
         <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
         <v>0.658</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
       </c>
       <c r="F21" t="n">
-        <v>8.300000000000001</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="22">
@@ -2105,19 +2105,19 @@
         <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
         <v>0.624</v>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="23">
@@ -2125,19 +2125,19 @@
         <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
         <v>0.132</v>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F23" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -2145,19 +2145,19 @@
         <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>0.148</v>
       </c>
       <c r="D24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="25">
@@ -2165,7 +2165,7 @@
         <v>44531</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
         <v>0.021</v>
@@ -2174,10 +2174,10 @@
         <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="26">
@@ -2191,13 +2191,13 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="27">
@@ -2205,19 +2205,19 @@
         <v>44593</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C27" t="n">
         <v>0.13</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="28">
@@ -2225,19 +2225,19 @@
         <v>44621</v>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C28" t="n">
         <v>0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F28" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -2245,19 +2245,19 @@
         <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C29" t="n">
         <v>0.141</v>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E29" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -2271,13 +2271,13 @@
         <v>0.408</v>
       </c>
       <c r="D30" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F30" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="31">
@@ -2285,7 +2285,7 @@
         <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C31" t="n">
         <v>0.6860000000000001</v>
@@ -2294,10 +2294,10 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F31" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -2305,19 +2305,19 @@
         <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C32" t="n">
         <v>0.753</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E32" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F32" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -2325,19 +2325,19 @@
         <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C33" t="n">
         <v>0.854</v>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F33" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -2345,19 +2345,19 @@
         <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C34" t="n">
         <v>0.449</v>
       </c>
       <c r="D34" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F34" t="n">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="35">
@@ -2365,19 +2365,19 @@
         <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C35" t="n">
         <v>0.017</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F35" t="n">
-        <v>7.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -2385,19 +2385,19 @@
         <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
         <v>0.17</v>
       </c>
       <c r="D36" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E36" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F36" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="37">
@@ -2411,13 +2411,13 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="38">
@@ -2431,13 +2431,13 @@
         <v>0.128</v>
       </c>
       <c r="D38" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -2445,19 +2445,19 @@
         <v>44958</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>8.699999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="40">
@@ -2465,7 +2465,7 @@
         <v>44986</v>
       </c>
       <c r="B40" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C40" t="n">
         <v>0.016</v>
@@ -2474,10 +2474,10 @@
         <v>17</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F40" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="41">
@@ -2491,13 +2491,13 @@
         <v>0.145</v>
       </c>
       <c r="D41" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E41" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F41" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="42">
@@ -2505,19 +2505,19 @@
         <v>45047</v>
       </c>
       <c r="B42" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C42" t="n">
         <v>0.545</v>
       </c>
       <c r="D42" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E42" t="n">
         <v>18</v>
       </c>
       <c r="F42" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -2525,19 +2525,19 @@
         <v>45078</v>
       </c>
       <c r="B43" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C43" t="n">
         <v>0.763</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F43" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="44">
@@ -2545,19 +2545,19 @@
         <v>45108</v>
       </c>
       <c r="B44" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C44" t="n">
         <v>0.842</v>
       </c>
       <c r="D44" t="n">
+        <v>9</v>
+      </c>
+      <c r="E44" t="n">
+        <v>16</v>
+      </c>
+      <c r="F44" t="n">
         <v>8</v>
-      </c>
-      <c r="E44" t="n">
-        <v>18</v>
-      </c>
-      <c r="F44" t="n">
-        <v>9.1</v>
       </c>
     </row>
     <row r="45">
@@ -2571,13 +2571,13 @@
         <v>0.74</v>
       </c>
       <c r="D45" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F45" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="46">
@@ -2585,19 +2585,19 @@
         <v>45170</v>
       </c>
       <c r="B46" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C46" t="n">
         <v>0.397</v>
       </c>
       <c r="D46" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="47">
@@ -2605,19 +2605,19 @@
         <v>45200</v>
       </c>
       <c r="B47" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C47" t="n">
         <v>0.115</v>
       </c>
       <c r="D47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F47" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="48">
@@ -2625,7 +2625,7 @@
         <v>45231</v>
       </c>
       <c r="B48" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
         <v>0.142</v>
@@ -2634,10 +2634,10 @@
         <v>19</v>
       </c>
       <c r="E48" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>8.699999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="49">
@@ -2651,13 +2651,13 @@
         <v>0.269</v>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="50">
@@ -2665,19 +2665,19 @@
         <v>45292</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C50" t="n">
         <v>0.217</v>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="51">
@@ -2691,13 +2691,13 @@
         <v>0.053</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F51" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2711,13 +2711,13 @@
         <v>0.223</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="53">
@@ -2731,13 +2731,13 @@
         <v>0.168</v>
       </c>
       <c r="D53" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E53" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F53" t="n">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="54">
@@ -2745,19 +2745,19 @@
         <v>45413</v>
       </c>
       <c r="B54" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C54" t="n">
         <v>0.496</v>
       </c>
       <c r="D54" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E54" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F54" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2765,19 +2765,19 @@
         <v>45444</v>
       </c>
       <c r="B55" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C55" t="n">
         <v>0.855</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F55" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="56">
@@ -2785,19 +2785,19 @@
         <v>45474</v>
       </c>
       <c r="B56" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C56" t="n">
         <v>0.981</v>
       </c>
       <c r="D56" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E56" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F56" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="57">
@@ -2805,19 +2805,19 @@
         <v>45505</v>
       </c>
       <c r="B57" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C57" t="n">
         <v>0.877</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E57" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F57" t="n">
-        <v>9.300000000000001</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="58">
@@ -2825,19 +2825,19 @@
         <v>45536</v>
       </c>
       <c r="B58" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C58" t="n">
         <v>0.476</v>
       </c>
       <c r="D58" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E58" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F58" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="59">
@@ -2845,19 +2845,19 @@
         <v>45566</v>
       </c>
       <c r="B59" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C59" t="n">
         <v>0.164</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F59" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="60">
@@ -2865,19 +2865,19 @@
         <v>45597</v>
       </c>
       <c r="B60" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C60" t="n">
         <v>0.21</v>
       </c>
       <c r="D60" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F60" t="n">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="61">
@@ -2885,19 +2885,19 @@
         <v>45627</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C61" t="n">
         <v>0.255</v>
       </c>
       <c r="D61" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E61" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F61" t="n">
-        <v>7.7</v>
+        <v>6.4</v>
       </c>
     </row>
   </sheetData>
@@ -2956,13 +2956,13 @@
         <v>43831</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C2" t="n">
         <v>0.19</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E2" t="n">
         <v>0.199</v>
@@ -2979,13 +2979,13 @@
         <v>43862</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
         <v>0.146</v>
       </c>
       <c r="D3" t="n">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="E3" t="n">
         <v>0.12</v>
@@ -3002,13 +3002,13 @@
         <v>43891</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
         <v>0.217</v>
       </c>
       <c r="D4" t="n">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="E4" t="n">
         <v>0.114</v>
@@ -3025,7 +3025,7 @@
         <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="C5" t="n">
         <v>0.294</v>
@@ -3048,13 +3048,13 @@
         <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="C6" t="n">
         <v>0.509</v>
       </c>
       <c r="D6" t="n">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="E6" t="n">
         <v>0.8110000000000001</v>
@@ -3071,13 +3071,13 @@
         <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="C7" t="n">
         <v>0.772</v>
       </c>
       <c r="D7" t="n">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="E7" t="n">
         <v>0.746</v>
@@ -3094,13 +3094,13 @@
         <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E8" t="n">
         <v>0.921</v>
@@ -3117,13 +3117,13 @@
         <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
         <v>0.861</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E9" t="n">
         <v>0.631</v>
@@ -3140,13 +3140,13 @@
         <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
         <v>0.509</v>
       </c>
       <c r="D10" t="n">
-        <v>130</v>
+        <v>72</v>
       </c>
       <c r="E10" t="n">
         <v>0.384</v>
@@ -3163,13 +3163,13 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
         <v>0.242</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="E11" t="n">
         <v>0.096</v>
@@ -3186,13 +3186,13 @@
         <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
         <v>0.163</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="E12" t="n">
         <v>0.058</v>
@@ -3215,7 +3215,7 @@
         <v>0.163</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>108</v>
       </c>
       <c r="E13" t="n">
         <v>0.196</v>
@@ -3232,13 +3232,13 @@
         <v>44197</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
         <v>0.218</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E14" t="n">
         <v>0.394</v>
@@ -3255,13 +3255,13 @@
         <v>44228</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="C15" t="n">
         <v>0.043</v>
       </c>
       <c r="D15" t="n">
-        <v>51</v>
+        <v>138</v>
       </c>
       <c r="E15" t="n">
         <v>0.097</v>
@@ -3284,7 +3284,7 @@
         <v>0.055</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E16" t="n">
         <v>0.269</v>
@@ -3301,13 +3301,13 @@
         <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="C17" t="n">
         <v>0.144</v>
       </c>
       <c r="D17" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E17" t="n">
         <v>0.305</v>
@@ -3324,13 +3324,13 @@
         <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="C18" t="n">
         <v>0.453</v>
       </c>
       <c r="D18" t="n">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="E18" t="n">
         <v>0.318</v>
@@ -3347,13 +3347,13 @@
         <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="C19" t="n">
         <v>0.8090000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="E19" t="n">
         <v>0.376</v>
@@ -3370,13 +3370,13 @@
         <v>44378</v>
       </c>
       <c r="B20" t="n">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="C20" t="n">
         <v>0.799</v>
       </c>
       <c r="D20" t="n">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="E20" t="n">
         <v>0.322</v>
@@ -3393,13 +3393,13 @@
         <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C21" t="n">
         <v>0.658</v>
       </c>
       <c r="D21" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E21" t="n">
         <v>0.745</v>
@@ -3416,13 +3416,13 @@
         <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="C22" t="n">
         <v>0.624</v>
       </c>
       <c r="D22" t="n">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="E22" t="n">
         <v>0.52</v>
@@ -3439,13 +3439,13 @@
         <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="C23" t="n">
         <v>0.132</v>
       </c>
       <c r="D23" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E23" t="n">
         <v>0.214</v>
@@ -3462,13 +3462,13 @@
         <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C24" t="n">
         <v>0.148</v>
       </c>
       <c r="D24" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="E24" t="n">
         <v>0.036</v>
@@ -3485,13 +3485,13 @@
         <v>44531</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C25" t="n">
         <v>0.021</v>
       </c>
       <c r="D25" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="E25" t="n">
         <v>0.334</v>
@@ -3514,7 +3514,7 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E26" t="n">
         <v>0.128</v>
@@ -3531,13 +3531,13 @@
         <v>44593</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C27" t="n">
         <v>0.13</v>
       </c>
       <c r="D27" t="n">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="E27" t="n">
         <v>0.075</v>
@@ -3554,13 +3554,13 @@
         <v>44621</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C28" t="n">
         <v>0.024</v>
       </c>
       <c r="D28" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="E28" t="n">
         <v>0.016</v>
@@ -3577,13 +3577,13 @@
         <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="C29" t="n">
         <v>0.141</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
         <v>0.236</v>
@@ -3600,13 +3600,13 @@
         <v>44682</v>
       </c>
       <c r="B30" t="n">
-        <v>90</v>
+        <v>39</v>
       </c>
       <c r="C30" t="n">
         <v>0.408</v>
       </c>
       <c r="D30" t="n">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="E30" t="n">
         <v>0.503</v>
@@ -3623,13 +3623,13 @@
         <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>93</v>
+        <v>40</v>
       </c>
       <c r="C31" t="n">
         <v>0.6860000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>136</v>
+        <v>72</v>
       </c>
       <c r="E31" t="n">
         <v>0.413</v>
@@ -3646,13 +3646,13 @@
         <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="C32" t="n">
         <v>0.753</v>
       </c>
       <c r="D32" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="E32" t="n">
         <v>0.951</v>
@@ -3669,13 +3669,13 @@
         <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C33" t="n">
         <v>0.854</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E33" t="n">
         <v>0.866</v>
@@ -3692,13 +3692,13 @@
         <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="C34" t="n">
         <v>0.449</v>
       </c>
       <c r="D34" t="n">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="E34" t="n">
         <v>0.743</v>
@@ -3715,13 +3715,13 @@
         <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="C35" t="n">
         <v>0.017</v>
       </c>
       <c r="D35" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="E35" t="n">
         <v>0.07000000000000001</v>
@@ -3738,13 +3738,13 @@
         <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C36" t="n">
         <v>0.17</v>
       </c>
       <c r="D36" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E36" t="n">
         <v>0.276</v>
@@ -3761,13 +3761,13 @@
         <v>44896</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C37" t="n">
         <v>0.008999999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E37" t="n">
         <v>0.155</v>
@@ -3784,13 +3784,13 @@
         <v>44927</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C38" t="n">
         <v>0.128</v>
       </c>
       <c r="D38" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E38" t="n">
         <v>0.375</v>
@@ -3807,13 +3807,13 @@
         <v>44958</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="E39" t="n">
         <v>0.055</v>
@@ -3836,7 +3836,7 @@
         <v>0.016</v>
       </c>
       <c r="D40" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E40" t="n">
         <v>0.136</v>
@@ -3853,13 +3853,13 @@
         <v>45017</v>
       </c>
       <c r="B41" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="C41" t="n">
         <v>0.145</v>
       </c>
       <c r="D41" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E41" t="n">
         <v>0.045</v>
@@ -3876,13 +3876,13 @@
         <v>45047</v>
       </c>
       <c r="B42" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C42" t="n">
         <v>0.545</v>
       </c>
       <c r="D42" t="n">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="E42" t="n">
         <v>0.523</v>
@@ -3899,13 +3899,13 @@
         <v>45078</v>
       </c>
       <c r="B43" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="C43" t="n">
         <v>0.763</v>
       </c>
       <c r="D43" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="E43" t="n">
         <v>0.377</v>
@@ -3922,13 +3922,13 @@
         <v>45108</v>
       </c>
       <c r="B44" t="n">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="C44" t="n">
         <v>0.842</v>
       </c>
       <c r="D44" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E44" t="n">
         <v>0.46</v>
@@ -3945,13 +3945,13 @@
         <v>45139</v>
       </c>
       <c r="B45" t="n">
-        <v>98</v>
+        <v>39</v>
       </c>
       <c r="C45" t="n">
         <v>0.74</v>
       </c>
       <c r="D45" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E45" t="n">
         <v>0.599</v>
@@ -3968,13 +3968,13 @@
         <v>45170</v>
       </c>
       <c r="B46" t="n">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="C46" t="n">
         <v>0.397</v>
       </c>
       <c r="D46" t="n">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="E46" t="n">
         <v>0.873</v>
@@ -3991,13 +3991,13 @@
         <v>45200</v>
       </c>
       <c r="B47" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="C47" t="n">
         <v>0.115</v>
       </c>
       <c r="D47" t="n">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="E47" t="n">
         <v>0.222</v>
@@ -4014,13 +4014,13 @@
         <v>45231</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C48" t="n">
         <v>0.142</v>
       </c>
       <c r="D48" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E48" t="n">
         <v>0.212</v>
@@ -4037,13 +4037,13 @@
         <v>45261</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="C49" t="n">
         <v>0.269</v>
       </c>
       <c r="D49" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E49" t="n">
         <v>0.097</v>
@@ -4060,13 +4060,13 @@
         <v>45292</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C50" t="n">
         <v>0.217</v>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E50" t="n">
         <v>0.037</v>
@@ -4089,7 +4089,7 @@
         <v>0.053</v>
       </c>
       <c r="D51" t="n">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="E51" t="n">
         <v>0.359</v>
@@ -4106,13 +4106,13 @@
         <v>45352</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="C52" t="n">
         <v>0.223</v>
       </c>
       <c r="D52" t="n">
-        <v>56</v>
+        <v>112</v>
       </c>
       <c r="E52" t="n">
         <v>0.36</v>
@@ -4129,13 +4129,13 @@
         <v>45383</v>
       </c>
       <c r="B53" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="C53" t="n">
         <v>0.168</v>
       </c>
       <c r="D53" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E53" t="n">
         <v>0.253</v>
@@ -4152,13 +4152,13 @@
         <v>45413</v>
       </c>
       <c r="B54" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C54" t="n">
         <v>0.496</v>
       </c>
       <c r="D54" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E54" t="n">
         <v>0.96</v>
@@ -4175,13 +4175,13 @@
         <v>45444</v>
       </c>
       <c r="B55" t="n">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="C55" t="n">
         <v>0.855</v>
       </c>
       <c r="D55" t="n">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="E55" t="n">
         <v>0.526</v>
@@ -4198,13 +4198,13 @@
         <v>45474</v>
       </c>
       <c r="B56" t="n">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="C56" t="n">
         <v>0.981</v>
       </c>
       <c r="D56" t="n">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="E56" t="n">
         <v>0.663</v>
@@ -4221,13 +4221,13 @@
         <v>45505</v>
       </c>
       <c r="B57" t="n">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="C57" t="n">
         <v>0.877</v>
       </c>
       <c r="D57" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E57" t="n">
         <v>0.792</v>
@@ -4244,13 +4244,13 @@
         <v>45536</v>
       </c>
       <c r="B58" t="n">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="C58" t="n">
         <v>0.476</v>
       </c>
       <c r="D58" t="n">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E58" t="n">
         <v>0.555</v>
@@ -4267,13 +4267,13 @@
         <v>45566</v>
       </c>
       <c r="B59" t="n">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="C59" t="n">
         <v>0.164</v>
       </c>
       <c r="D59" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="E59" t="n">
         <v>0.312</v>
@@ -4290,13 +4290,13 @@
         <v>45597</v>
       </c>
       <c r="B60" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C60" t="n">
         <v>0.21</v>
       </c>
       <c r="D60" t="n">
-        <v>130</v>
+        <v>84</v>
       </c>
       <c r="E60" t="n">
         <v>0.257</v>
@@ -4313,13 +4313,13 @@
         <v>45627</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="C61" t="n">
         <v>0.255</v>
       </c>
       <c r="D61" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="E61" t="n">
         <v>0.034</v>

--- a/inputs/data/data.xlsx
+++ b/inputs/data/data.xlsx
@@ -459,7 +459,7 @@
         <v>43831</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
         <v>0.19</v>
@@ -479,7 +479,7 @@
         <v>43862</v>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0.146</v>
@@ -488,7 +488,7 @@
         <v>27</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F3" t="n">
         <v>6.7</v>
@@ -499,7 +499,7 @@
         <v>43891</v>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
         <v>0.217</v>
@@ -508,7 +508,7 @@
         <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>2.4</v>
@@ -519,7 +519,7 @@
         <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>0.294</v>
@@ -528,7 +528,7 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F5" t="n">
         <v>4.5</v>
@@ -539,7 +539,7 @@
         <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
         <v>0.509</v>
@@ -548,7 +548,7 @@
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" t="n">
         <v>6.1</v>
@@ -559,7 +559,7 @@
         <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
         <v>0.772</v>
@@ -568,7 +568,7 @@
         <v>28</v>
       </c>
       <c r="E7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
         <v>4.8</v>
@@ -579,7 +579,7 @@
         <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -588,7 +588,7 @@
         <v>20</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
         <v>4.9</v>
@@ -599,7 +599,7 @@
         <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>0.861</v>
@@ -608,7 +608,7 @@
         <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
         <v>3.3</v>
@@ -619,7 +619,7 @@
         <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>0.509</v>
@@ -628,7 +628,7 @@
         <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
         <v>3.7</v>
@@ -639,7 +639,7 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
         <v>0.242</v>
@@ -648,7 +648,7 @@
         <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
         <v>3.3</v>
@@ -659,7 +659,7 @@
         <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
         <v>0.163</v>
@@ -668,7 +668,7 @@
         <v>13</v>
       </c>
       <c r="E12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
@@ -688,7 +688,7 @@
         <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
         <v>4.3</v>
@@ -719,7 +719,7 @@
         <v>44228</v>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
         <v>0.043</v>
@@ -739,7 +739,7 @@
         <v>44256</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
         <v>0.055</v>
@@ -748,7 +748,7 @@
         <v>14</v>
       </c>
       <c r="E16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F16" t="n">
         <v>4.8</v>
@@ -759,7 +759,7 @@
         <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
         <v>0.144</v>
@@ -768,7 +768,7 @@
         <v>22</v>
       </c>
       <c r="E17" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F17" t="n">
         <v>5</v>
@@ -779,7 +779,7 @@
         <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
         <v>0.453</v>
@@ -788,7 +788,7 @@
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F18" t="n">
         <v>5.8</v>
@@ -799,7 +799,7 @@
         <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
         <v>0.8090000000000001</v>
@@ -808,7 +808,7 @@
         <v>18</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
         <v>4.5</v>
@@ -828,7 +828,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" t="n">
         <v>4.8</v>
@@ -839,7 +839,7 @@
         <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
         <v>0.658</v>
@@ -859,7 +859,7 @@
         <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
         <v>0.624</v>
@@ -868,7 +868,7 @@
         <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F22" t="n">
         <v>4.7</v>
@@ -879,7 +879,7 @@
         <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
         <v>0.132</v>
@@ -888,7 +888,7 @@
         <v>15</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
         <v>3.1</v>
@@ -899,7 +899,7 @@
         <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>0.148</v>
@@ -908,7 +908,7 @@
         <v>15</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F24" t="n">
         <v>5.1</v>
@@ -928,7 +928,7 @@
         <v>13</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>3.5</v>
@@ -959,7 +959,7 @@
         <v>44593</v>
       </c>
       <c r="B27" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>0.13</v>
@@ -979,7 +979,7 @@
         <v>44621</v>
       </c>
       <c r="B28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C28" t="n">
         <v>0.024</v>
@@ -988,7 +988,7 @@
         <v>15</v>
       </c>
       <c r="E28" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>3.1</v>
@@ -999,7 +999,7 @@
         <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C29" t="n">
         <v>0.141</v>
@@ -1008,7 +1008,7 @@
         <v>13</v>
       </c>
       <c r="E29" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
         <v>5.1</v>
@@ -1019,7 +1019,7 @@
         <v>44682</v>
       </c>
       <c r="B30" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C30" t="n">
         <v>0.408</v>
@@ -1028,7 +1028,7 @@
         <v>5</v>
       </c>
       <c r="E30" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F30" t="n">
         <v>5.4</v>
@@ -1039,7 +1039,7 @@
         <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C31" t="n">
         <v>0.6860000000000001</v>
@@ -1048,7 +1048,7 @@
         <v>19</v>
       </c>
       <c r="E31" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F31" t="n">
         <v>7</v>
@@ -1059,7 +1059,7 @@
         <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C32" t="n">
         <v>0.753</v>
@@ -1068,7 +1068,7 @@
         <v>15</v>
       </c>
       <c r="E32" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F32" t="n">
         <v>4.9</v>
@@ -1079,7 +1079,7 @@
         <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C33" t="n">
         <v>0.854</v>
@@ -1088,7 +1088,7 @@
         <v>18</v>
       </c>
       <c r="E33" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F33" t="n">
         <v>3.7</v>
@@ -1108,7 +1108,7 @@
         <v>4</v>
       </c>
       <c r="E34" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F34" t="n">
         <v>4.6</v>
@@ -1119,7 +1119,7 @@
         <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C35" t="n">
         <v>0.017</v>
@@ -1139,7 +1139,7 @@
         <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C36" t="n">
         <v>0.17</v>
@@ -1148,7 +1148,7 @@
         <v>13</v>
       </c>
       <c r="E36" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F36" t="n">
         <v>3.9</v>
@@ -1159,7 +1159,7 @@
         <v>44896</v>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C37" t="n">
         <v>0.008999999999999999</v>
@@ -1168,7 +1168,7 @@
         <v>25</v>
       </c>
       <c r="E37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F37" t="n">
         <v>4.9</v>
@@ -1188,7 +1188,7 @@
         <v>4</v>
       </c>
       <c r="E38" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F38" t="n">
         <v>2.7</v>
@@ -1199,7 +1199,7 @@
         <v>44958</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>26</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F40" t="n">
         <v>5.8</v>
@@ -1259,7 +1259,7 @@
         <v>45047</v>
       </c>
       <c r="B42" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C42" t="n">
         <v>0.545</v>
@@ -1279,7 +1279,7 @@
         <v>45078</v>
       </c>
       <c r="B43" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C43" t="n">
         <v>0.763</v>
@@ -1288,7 +1288,7 @@
         <v>16</v>
       </c>
       <c r="E43" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F43" t="n">
         <v>7</v>
@@ -1308,7 +1308,7 @@
         <v>25</v>
       </c>
       <c r="E44" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F44" t="n">
         <v>4.7</v>
@@ -1319,7 +1319,7 @@
         <v>45139</v>
       </c>
       <c r="B45" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C45" t="n">
         <v>0.74</v>
@@ -1339,7 +1339,7 @@
         <v>45170</v>
       </c>
       <c r="B46" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C46" t="n">
         <v>0.397</v>
@@ -1348,7 +1348,7 @@
         <v>6</v>
       </c>
       <c r="E46" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F46" t="n">
         <v>3.1</v>
@@ -1368,7 +1368,7 @@
         <v>15</v>
       </c>
       <c r="E47" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F47" t="n">
         <v>2.5</v>
@@ -1379,7 +1379,7 @@
         <v>45231</v>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C48" t="n">
         <v>0.142</v>
@@ -1399,7 +1399,7 @@
         <v>45261</v>
       </c>
       <c r="B49" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C49" t="n">
         <v>0.269</v>
@@ -1408,7 +1408,7 @@
         <v>20</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
         <v>3</v>
@@ -1419,7 +1419,7 @@
         <v>45292</v>
       </c>
       <c r="B50" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
         <v>0.217</v>
@@ -1428,7 +1428,7 @@
         <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>4.6</v>
@@ -1439,7 +1439,7 @@
         <v>45323</v>
       </c>
       <c r="B51" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
         <v>0.053</v>
@@ -1448,7 +1448,7 @@
         <v>18</v>
       </c>
       <c r="E51" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>4.4</v>
@@ -1459,7 +1459,7 @@
         <v>45352</v>
       </c>
       <c r="B52" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C52" t="n">
         <v>0.223</v>
@@ -1468,7 +1468,7 @@
         <v>19</v>
       </c>
       <c r="E52" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>5.9</v>
@@ -1488,7 +1488,7 @@
         <v>24</v>
       </c>
       <c r="E53" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F53" t="n">
         <v>5.9</v>
@@ -1499,7 +1499,7 @@
         <v>45413</v>
       </c>
       <c r="B54" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C54" t="n">
         <v>0.496</v>
@@ -1528,7 +1528,7 @@
         <v>16</v>
       </c>
       <c r="E55" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F55" t="n">
         <v>4.4</v>
@@ -1539,7 +1539,7 @@
         <v>45474</v>
       </c>
       <c r="B56" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C56" t="n">
         <v>0.981</v>
@@ -1559,7 +1559,7 @@
         <v>45505</v>
       </c>
       <c r="B57" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C57" t="n">
         <v>0.877</v>
@@ -1568,7 +1568,7 @@
         <v>26</v>
       </c>
       <c r="E57" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F57" t="n">
         <v>2.8</v>
@@ -1579,7 +1579,7 @@
         <v>45536</v>
       </c>
       <c r="B58" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C58" t="n">
         <v>0.476</v>
@@ -1588,7 +1588,7 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F58" t="n">
         <v>3.1</v>
@@ -1599,7 +1599,7 @@
         <v>45566</v>
       </c>
       <c r="B59" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C59" t="n">
         <v>0.164</v>
@@ -1608,7 +1608,7 @@
         <v>21</v>
       </c>
       <c r="E59" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F59" t="n">
         <v>4</v>
@@ -1619,7 +1619,7 @@
         <v>45597</v>
       </c>
       <c r="B60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C60" t="n">
         <v>0.21</v>
@@ -1628,7 +1628,7 @@
         <v>14</v>
       </c>
       <c r="E60" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F60" t="n">
         <v>4.5</v>
@@ -1639,7 +1639,7 @@
         <v>45627</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C61" t="n">
         <v>0.255</v>
@@ -1648,7 +1648,7 @@
         <v>19</v>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F61" t="n">
         <v>2.9</v>
@@ -1725,7 +1725,7 @@
         <v>43862</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>0.146</v>
@@ -1745,7 +1745,7 @@
         <v>43891</v>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>0.217</v>
@@ -1754,7 +1754,7 @@
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
         <v>8</v>
@@ -1765,7 +1765,7 @@
         <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
         <v>0.294</v>
@@ -1774,7 +1774,7 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
         <v>9.4</v>
@@ -1785,7 +1785,7 @@
         <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
         <v>0.509</v>
@@ -1794,7 +1794,7 @@
         <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F6" t="n">
         <v>8.199999999999999</v>
@@ -1805,7 +1805,7 @@
         <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
         <v>0.772</v>
@@ -1814,7 +1814,7 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F7" t="n">
         <v>8.5</v>
@@ -1825,7 +1825,7 @@
         <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -1834,7 +1834,7 @@
         <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="n">
         <v>10</v>
@@ -1845,7 +1845,7 @@
         <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
         <v>0.861</v>
@@ -1854,7 +1854,7 @@
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F9" t="n">
         <v>7.5</v>
@@ -1865,7 +1865,7 @@
         <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
         <v>0.509</v>
@@ -1874,7 +1874,7 @@
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>8.199999999999999</v>
@@ -1885,7 +1885,7 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
         <v>0.242</v>
@@ -1894,7 +1894,7 @@
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
         <v>6.6</v>
@@ -1905,7 +1905,7 @@
         <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
         <v>0.163</v>
@@ -1914,7 +1914,7 @@
         <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
         <v>7.3</v>
@@ -1934,7 +1934,7 @@
         <v>15</v>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
         <v>9</v>
@@ -1945,7 +1945,7 @@
         <v>44197</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
         <v>0.218</v>
@@ -1965,7 +1965,7 @@
         <v>44228</v>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0.043</v>
@@ -1974,7 +1974,7 @@
         <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F15" t="n">
         <v>9.800000000000001</v>
@@ -1985,7 +1985,7 @@
         <v>44256</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>0.055</v>
@@ -1994,7 +1994,7 @@
         <v>9</v>
       </c>
       <c r="E16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>9.300000000000001</v>
@@ -2005,7 +2005,7 @@
         <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
         <v>0.144</v>
@@ -2014,7 +2014,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
         <v>8.4</v>
@@ -2025,7 +2025,7 @@
         <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
         <v>0.453</v>
@@ -2034,7 +2034,7 @@
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F18" t="n">
         <v>9.199999999999999</v>
@@ -2045,7 +2045,7 @@
         <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>0.8090000000000001</v>
@@ -2054,7 +2054,7 @@
         <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
         <v>9.199999999999999</v>
@@ -2065,7 +2065,7 @@
         <v>44378</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
         <v>0.799</v>
@@ -2074,7 +2074,7 @@
         <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
         <v>8.5</v>
@@ -2085,7 +2085,7 @@
         <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
         <v>0.658</v>
@@ -2094,7 +2094,7 @@
         <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F21" t="n">
         <v>6.3</v>
@@ -2105,7 +2105,7 @@
         <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
         <v>0.624</v>
@@ -2114,7 +2114,7 @@
         <v>15</v>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F22" t="n">
         <v>6.7</v>
@@ -2125,7 +2125,7 @@
         <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" t="n">
         <v>0.132</v>
@@ -2134,7 +2134,7 @@
         <v>6</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F23" t="n">
         <v>7</v>
@@ -2154,7 +2154,7 @@
         <v>18</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>7.2</v>
@@ -2165,7 +2165,7 @@
         <v>44531</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0.021</v>
@@ -2194,7 +2194,7 @@
         <v>14</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>8.1</v>
@@ -2205,7 +2205,7 @@
         <v>44593</v>
       </c>
       <c r="B27" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C27" t="n">
         <v>0.13</v>
@@ -2225,7 +2225,7 @@
         <v>44621</v>
       </c>
       <c r="B28" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C28" t="n">
         <v>0.024</v>
@@ -2234,7 +2234,7 @@
         <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F28" t="n">
         <v>9</v>
@@ -2245,7 +2245,7 @@
         <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C29" t="n">
         <v>0.141</v>
@@ -2254,7 +2254,7 @@
         <v>15</v>
       </c>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F29" t="n">
         <v>9.300000000000001</v>
@@ -2265,7 +2265,7 @@
         <v>44682</v>
       </c>
       <c r="B30" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C30" t="n">
         <v>0.408</v>
@@ -2274,7 +2274,7 @@
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F30" t="n">
         <v>9.1</v>
@@ -2285,7 +2285,7 @@
         <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C31" t="n">
         <v>0.6860000000000001</v>
@@ -2294,7 +2294,7 @@
         <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F31" t="n">
         <v>9.300000000000001</v>
@@ -2305,7 +2305,7 @@
         <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C32" t="n">
         <v>0.753</v>
@@ -2314,7 +2314,7 @@
         <v>20</v>
       </c>
       <c r="E32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F32" t="n">
         <v>8.699999999999999</v>
@@ -2325,7 +2325,7 @@
         <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" t="n">
         <v>0.854</v>
@@ -2334,7 +2334,7 @@
         <v>21</v>
       </c>
       <c r="E33" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F33" t="n">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C34" t="n">
         <v>0.449</v>
@@ -2354,7 +2354,7 @@
         <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F34" t="n">
         <v>7.3</v>
@@ -2365,7 +2365,7 @@
         <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
         <v>0.017</v>
@@ -2374,7 +2374,7 @@
         <v>6</v>
       </c>
       <c r="E35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>6</v>
@@ -2385,7 +2385,7 @@
         <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
         <v>0.17</v>
@@ -2394,7 +2394,7 @@
         <v>16</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F36" t="n">
         <v>7.7</v>
@@ -2414,7 +2414,7 @@
         <v>12</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F37" t="n">
         <v>7.8</v>
@@ -2445,7 +2445,7 @@
         <v>44958</v>
       </c>
       <c r="B39" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -2465,7 +2465,7 @@
         <v>44986</v>
       </c>
       <c r="B40" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C40" t="n">
         <v>0.016</v>
@@ -2474,7 +2474,7 @@
         <v>17</v>
       </c>
       <c r="E40" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F40" t="n">
         <v>7.8</v>
@@ -2485,7 +2485,7 @@
         <v>45017</v>
       </c>
       <c r="B41" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C41" t="n">
         <v>0.145</v>
@@ -2494,7 +2494,7 @@
         <v>16</v>
       </c>
       <c r="E41" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F41" t="n">
         <v>9.6</v>
@@ -2505,7 +2505,7 @@
         <v>45047</v>
       </c>
       <c r="B42" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C42" t="n">
         <v>0.545</v>
@@ -2514,7 +2514,7 @@
         <v>5</v>
       </c>
       <c r="E42" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F42" t="n">
         <v>8.699999999999999</v>
@@ -2525,7 +2525,7 @@
         <v>45078</v>
       </c>
       <c r="B43" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C43" t="n">
         <v>0.763</v>
@@ -2534,7 +2534,7 @@
         <v>2</v>
       </c>
       <c r="E43" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F43" t="n">
         <v>8.9</v>
@@ -2545,7 +2545,7 @@
         <v>45108</v>
       </c>
       <c r="B44" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C44" t="n">
         <v>0.842</v>
@@ -2554,7 +2554,7 @@
         <v>9</v>
       </c>
       <c r="E44" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F44" t="n">
         <v>8</v>
@@ -2565,7 +2565,7 @@
         <v>45139</v>
       </c>
       <c r="B45" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C45" t="n">
         <v>0.74</v>
@@ -2574,7 +2574,7 @@
         <v>16</v>
       </c>
       <c r="E45" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F45" t="n">
         <v>7.6</v>
@@ -2585,7 +2585,7 @@
         <v>45170</v>
       </c>
       <c r="B46" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C46" t="n">
         <v>0.397</v>
@@ -2594,7 +2594,7 @@
         <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F46" t="n">
         <v>8.1</v>
@@ -2605,7 +2605,7 @@
         <v>45200</v>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C47" t="n">
         <v>0.115</v>
@@ -2614,7 +2614,7 @@
         <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F47" t="n">
         <v>6.8</v>
@@ -2625,7 +2625,7 @@
         <v>45231</v>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C48" t="n">
         <v>0.142</v>
@@ -2634,7 +2634,7 @@
         <v>19</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F48" t="n">
         <v>7.4</v>
@@ -2654,7 +2654,7 @@
         <v>8</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
         <v>7.2</v>
@@ -2665,7 +2665,7 @@
         <v>45292</v>
       </c>
       <c r="B50" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C50" t="n">
         <v>0.217</v>
@@ -2685,7 +2685,7 @@
         <v>45323</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="C51" t="n">
         <v>0.053</v>
@@ -2694,7 +2694,7 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>8.199999999999999</v>
@@ -2714,7 +2714,7 @@
         <v>7</v>
       </c>
       <c r="E52" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F52" t="n">
         <v>8.9</v>
@@ -2745,7 +2745,7 @@
         <v>45413</v>
       </c>
       <c r="B54" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C54" t="n">
         <v>0.496</v>
@@ -2765,7 +2765,7 @@
         <v>45444</v>
       </c>
       <c r="B55" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C55" t="n">
         <v>0.855</v>
@@ -2774,7 +2774,7 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F55" t="n">
         <v>7.7</v>
@@ -2785,7 +2785,7 @@
         <v>45474</v>
       </c>
       <c r="B56" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C56" t="n">
         <v>0.981</v>
@@ -2794,7 +2794,7 @@
         <v>19</v>
       </c>
       <c r="E56" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F56" t="n">
         <v>7.9</v>
@@ -2805,7 +2805,7 @@
         <v>45505</v>
       </c>
       <c r="B57" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C57" t="n">
         <v>0.877</v>
@@ -2814,7 +2814,7 @@
         <v>12</v>
       </c>
       <c r="E57" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F57" t="n">
         <v>7.2</v>
@@ -2825,7 +2825,7 @@
         <v>45536</v>
       </c>
       <c r="B58" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C58" t="n">
         <v>0.476</v>
@@ -2834,7 +2834,7 @@
         <v>16</v>
       </c>
       <c r="E58" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F58" t="n">
         <v>8.5</v>
@@ -2845,7 +2845,7 @@
         <v>45566</v>
       </c>
       <c r="B59" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C59" t="n">
         <v>0.164</v>
@@ -2854,7 +2854,7 @@
         <v>3</v>
       </c>
       <c r="E59" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F59" t="n">
         <v>7.4</v>
@@ -2865,7 +2865,7 @@
         <v>45597</v>
       </c>
       <c r="B60" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C60" t="n">
         <v>0.21</v>
@@ -2874,7 +2874,7 @@
         <v>10</v>
       </c>
       <c r="E60" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F60" t="n">
         <v>8.1</v>
@@ -2885,7 +2885,7 @@
         <v>45627</v>
       </c>
       <c r="B61" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C61" t="n">
         <v>0.255</v>
@@ -2894,7 +2894,7 @@
         <v>20</v>
       </c>
       <c r="E61" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F61" t="n">
         <v>6.4</v>
@@ -3025,7 +3025,7 @@
         <v>43922</v>
       </c>
       <c r="B5" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C5" t="n">
         <v>0.294</v>
@@ -3048,7 +3048,7 @@
         <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="C6" t="n">
         <v>0.509</v>
@@ -3071,7 +3071,7 @@
         <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C7" t="n">
         <v>0.772</v>
@@ -3094,7 +3094,7 @@
         <v>44013</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -3117,7 +3117,7 @@
         <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
         <v>0.861</v>
@@ -3232,7 +3232,7 @@
         <v>44197</v>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C14" t="n">
         <v>0.218</v>
@@ -3255,7 +3255,7 @@
         <v>44228</v>
       </c>
       <c r="B15" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C15" t="n">
         <v>0.043</v>
@@ -3301,7 +3301,7 @@
         <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C17" t="n">
         <v>0.144</v>
@@ -3324,7 +3324,7 @@
         <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C18" t="n">
         <v>0.453</v>
@@ -3347,7 +3347,7 @@
         <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C19" t="n">
         <v>0.8090000000000001</v>
@@ -3370,7 +3370,7 @@
         <v>44378</v>
       </c>
       <c r="B20" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C20" t="n">
         <v>0.799</v>
@@ -3393,7 +3393,7 @@
         <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C21" t="n">
         <v>0.658</v>
@@ -3416,7 +3416,7 @@
         <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C22" t="n">
         <v>0.624</v>
@@ -3439,7 +3439,7 @@
         <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C23" t="n">
         <v>0.132</v>
@@ -3462,7 +3462,7 @@
         <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C24" t="n">
         <v>0.148</v>
@@ -3485,7 +3485,7 @@
         <v>44531</v>
       </c>
       <c r="B25" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C25" t="n">
         <v>0.021</v>
@@ -3531,7 +3531,7 @@
         <v>44593</v>
       </c>
       <c r="B27" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C27" t="n">
         <v>0.13</v>
@@ -3577,7 +3577,7 @@
         <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C29" t="n">
         <v>0.141</v>
@@ -3600,7 +3600,7 @@
         <v>44682</v>
       </c>
       <c r="B30" t="n">
-        <v>39</v>
+        <v>71</v>
       </c>
       <c r="C30" t="n">
         <v>0.408</v>
@@ -3623,7 +3623,7 @@
         <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C31" t="n">
         <v>0.6860000000000001</v>
@@ -3646,7 +3646,7 @@
         <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C32" t="n">
         <v>0.753</v>
@@ -3669,7 +3669,7 @@
         <v>44774</v>
       </c>
       <c r="B33" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C33" t="n">
         <v>0.854</v>
@@ -3692,7 +3692,7 @@
         <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C34" t="n">
         <v>0.449</v>
@@ -3715,7 +3715,7 @@
         <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C35" t="n">
         <v>0.017</v>
@@ -3738,7 +3738,7 @@
         <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C36" t="n">
         <v>0.17</v>
@@ -3761,7 +3761,7 @@
         <v>44896</v>
       </c>
       <c r="B37" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C37" t="n">
         <v>0.008999999999999999</v>
@@ -3784,7 +3784,7 @@
         <v>44927</v>
       </c>
       <c r="B38" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C38" t="n">
         <v>0.128</v>
@@ -3807,7 +3807,7 @@
         <v>44958</v>
       </c>
       <c r="B39" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -3853,7 +3853,7 @@
         <v>45017</v>
       </c>
       <c r="B41" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C41" t="n">
         <v>0.145</v>
@@ -3876,7 +3876,7 @@
         <v>45047</v>
       </c>
       <c r="B42" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C42" t="n">
         <v>0.545</v>
@@ -3899,7 +3899,7 @@
         <v>45078</v>
       </c>
       <c r="B43" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C43" t="n">
         <v>0.763</v>
@@ -3922,7 +3922,7 @@
         <v>45108</v>
       </c>
       <c r="B44" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C44" t="n">
         <v>0.842</v>
@@ -3945,7 +3945,7 @@
         <v>45139</v>
       </c>
       <c r="B45" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C45" t="n">
         <v>0.74</v>
@@ -3968,7 +3968,7 @@
         <v>45170</v>
       </c>
       <c r="B46" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C46" t="n">
         <v>0.397</v>
@@ -3991,7 +3991,7 @@
         <v>45200</v>
       </c>
       <c r="B47" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C47" t="n">
         <v>0.115</v>
@@ -4014,7 +4014,7 @@
         <v>45231</v>
       </c>
       <c r="B48" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C48" t="n">
         <v>0.142</v>
@@ -4037,7 +4037,7 @@
         <v>45261</v>
       </c>
       <c r="B49" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C49" t="n">
         <v>0.269</v>
@@ -4060,7 +4060,7 @@
         <v>45292</v>
       </c>
       <c r="B50" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C50" t="n">
         <v>0.217</v>
@@ -4106,7 +4106,7 @@
         <v>45352</v>
       </c>
       <c r="B52" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C52" t="n">
         <v>0.223</v>
@@ -4129,7 +4129,7 @@
         <v>45383</v>
       </c>
       <c r="B53" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C53" t="n">
         <v>0.168</v>
@@ -4175,7 +4175,7 @@
         <v>45444</v>
       </c>
       <c r="B55" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C55" t="n">
         <v>0.855</v>
@@ -4198,7 +4198,7 @@
         <v>45474</v>
       </c>
       <c r="B56" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C56" t="n">
         <v>0.981</v>
@@ -4221,7 +4221,7 @@
         <v>45505</v>
       </c>
       <c r="B57" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C57" t="n">
         <v>0.877</v>
@@ -4244,7 +4244,7 @@
         <v>45536</v>
       </c>
       <c r="B58" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C58" t="n">
         <v>0.476</v>
@@ -4267,7 +4267,7 @@
         <v>45566</v>
       </c>
       <c r="B59" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C59" t="n">
         <v>0.164</v>
@@ -4290,7 +4290,7 @@
         <v>45597</v>
       </c>
       <c r="B60" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C60" t="n">
         <v>0.21</v>
@@ -4313,7 +4313,7 @@
         <v>45627</v>
       </c>
       <c r="B61" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C61" t="n">
         <v>0.255</v>

--- a/inputs/data/data.xlsx
+++ b/inputs/data/data.xlsx
@@ -2956,7 +2956,7 @@
         <v>43831</v>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
         <v>0.19</v>
@@ -2979,7 +2979,7 @@
         <v>43862</v>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
         <v>0.146</v>
@@ -3002,7 +3002,7 @@
         <v>43891</v>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
         <v>0.217</v>
@@ -3048,7 +3048,7 @@
         <v>43952</v>
       </c>
       <c r="B6" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="C6" t="n">
         <v>0.509</v>
@@ -3071,7 +3071,7 @@
         <v>43983</v>
       </c>
       <c r="B7" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C7" t="n">
         <v>0.772</v>
@@ -3117,7 +3117,7 @@
         <v>44044</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
         <v>0.861</v>
@@ -3140,7 +3140,7 @@
         <v>44075</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C10" t="n">
         <v>0.509</v>
@@ -3163,7 +3163,7 @@
         <v>44105</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
         <v>0.242</v>
@@ -3186,7 +3186,7 @@
         <v>44136</v>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
         <v>0.163</v>
@@ -3232,7 +3232,7 @@
         <v>44197</v>
       </c>
       <c r="B14" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C14" t="n">
         <v>0.218</v>
@@ -3255,7 +3255,7 @@
         <v>44228</v>
       </c>
       <c r="B15" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
         <v>0.043</v>
@@ -3301,7 +3301,7 @@
         <v>44287</v>
       </c>
       <c r="B17" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" t="n">
         <v>0.144</v>
@@ -3324,7 +3324,7 @@
         <v>44317</v>
       </c>
       <c r="B18" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" t="n">
         <v>0.453</v>
@@ -3347,7 +3347,7 @@
         <v>44348</v>
       </c>
       <c r="B19" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C19" t="n">
         <v>0.8090000000000001</v>
@@ -3370,7 +3370,7 @@
         <v>44378</v>
       </c>
       <c r="B20" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C20" t="n">
         <v>0.799</v>
@@ -3393,7 +3393,7 @@
         <v>44409</v>
       </c>
       <c r="B21" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="C21" t="n">
         <v>0.658</v>
@@ -3416,7 +3416,7 @@
         <v>44440</v>
       </c>
       <c r="B22" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C22" t="n">
         <v>0.624</v>
@@ -3439,7 +3439,7 @@
         <v>44470</v>
       </c>
       <c r="B23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C23" t="n">
         <v>0.132</v>
@@ -3462,7 +3462,7 @@
         <v>44501</v>
       </c>
       <c r="B24" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C24" t="n">
         <v>0.148</v>
@@ -3485,7 +3485,7 @@
         <v>44531</v>
       </c>
       <c r="B25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C25" t="n">
         <v>0.021</v>
@@ -3531,7 +3531,7 @@
         <v>44593</v>
       </c>
       <c r="B27" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C27" t="n">
         <v>0.13</v>
@@ -3554,7 +3554,7 @@
         <v>44621</v>
       </c>
       <c r="B28" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C28" t="n">
         <v>0.024</v>
@@ -3577,7 +3577,7 @@
         <v>44652</v>
       </c>
       <c r="B29" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C29" t="n">
         <v>0.141</v>
@@ -3600,7 +3600,7 @@
         <v>44682</v>
       </c>
       <c r="B30" t="n">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="C30" t="n">
         <v>0.408</v>
@@ -3623,7 +3623,7 @@
         <v>44713</v>
       </c>
       <c r="B31" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C31" t="n">
         <v>0.6860000000000001</v>
@@ -3646,7 +3646,7 @@
         <v>44743</v>
       </c>
       <c r="B32" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C32" t="n">
         <v>0.753</v>
@@ -3692,7 +3692,7 @@
         <v>44805</v>
       </c>
       <c r="B34" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C34" t="n">
         <v>0.449</v>
@@ -3715,7 +3715,7 @@
         <v>44835</v>
       </c>
       <c r="B35" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C35" t="n">
         <v>0.017</v>
@@ -3738,7 +3738,7 @@
         <v>44866</v>
       </c>
       <c r="B36" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C36" t="n">
         <v>0.17</v>
@@ -3761,7 +3761,7 @@
         <v>44896</v>
       </c>
       <c r="B37" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C37" t="n">
         <v>0.008999999999999999</v>
@@ -3784,7 +3784,7 @@
         <v>44927</v>
       </c>
       <c r="B38" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C38" t="n">
         <v>0.128</v>
@@ -3807,7 +3807,7 @@
         <v>44958</v>
       </c>
       <c r="B39" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -3853,7 +3853,7 @@
         <v>45017</v>
       </c>
       <c r="B41" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C41" t="n">
         <v>0.145</v>
@@ -3876,7 +3876,7 @@
         <v>45047</v>
       </c>
       <c r="B42" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C42" t="n">
         <v>0.545</v>
@@ -3899,7 +3899,7 @@
         <v>45078</v>
       </c>
       <c r="B43" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C43" t="n">
         <v>0.763</v>
@@ -3922,7 +3922,7 @@
         <v>45108</v>
       </c>
       <c r="B44" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="C44" t="n">
         <v>0.842</v>
@@ -3945,7 +3945,7 @@
         <v>45139</v>
       </c>
       <c r="B45" t="n">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C45" t="n">
         <v>0.74</v>
@@ -3968,7 +3968,7 @@
         <v>45170</v>
       </c>
       <c r="B46" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C46" t="n">
         <v>0.397</v>
@@ -3991,7 +3991,7 @@
         <v>45200</v>
       </c>
       <c r="B47" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C47" t="n">
         <v>0.115</v>
@@ -4014,7 +4014,7 @@
         <v>45231</v>
       </c>
       <c r="B48" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C48" t="n">
         <v>0.142</v>
@@ -4060,7 +4060,7 @@
         <v>45292</v>
       </c>
       <c r="B50" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C50" t="n">
         <v>0.217</v>
@@ -4106,7 +4106,7 @@
         <v>45352</v>
       </c>
       <c r="B52" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C52" t="n">
         <v>0.223</v>
@@ -4129,7 +4129,7 @@
         <v>45383</v>
       </c>
       <c r="B53" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C53" t="n">
         <v>0.168</v>
@@ -4175,7 +4175,7 @@
         <v>45444</v>
       </c>
       <c r="B55" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C55" t="n">
         <v>0.855</v>
@@ -4198,7 +4198,7 @@
         <v>45474</v>
       </c>
       <c r="B56" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C56" t="n">
         <v>0.981</v>
@@ -4221,7 +4221,7 @@
         <v>45505</v>
       </c>
       <c r="B57" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C57" t="n">
         <v>0.877</v>
@@ -4244,7 +4244,7 @@
         <v>45536</v>
       </c>
       <c r="B58" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C58" t="n">
         <v>0.476</v>
@@ -4267,7 +4267,7 @@
         <v>45566</v>
       </c>
       <c r="B59" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C59" t="n">
         <v>0.164</v>
@@ -4290,7 +4290,7 @@
         <v>45597</v>
       </c>
       <c r="B60" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C60" t="n">
         <v>0.21</v>
@@ -4313,7 +4313,7 @@
         <v>45627</v>
       </c>
       <c r="B61" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C61" t="n">
         <v>0.255</v>
